--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44061</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>44551</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44258</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>44641</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45026</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45400</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44822</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44083</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45716.43703703704</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>44490</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>44468</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45715</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44098</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>44235</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>44235</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44280</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>44278</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>44053</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44455</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44295</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44341</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45324</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>45016</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45399</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>45566</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44980</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44942</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45147</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44319</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>44526</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>45595</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45400</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45191</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45239</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44876</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45450</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45328</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44417</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44060</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44229</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44083</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44353</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44337</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44411</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44449</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44477</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44564</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44827</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44193</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44215</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44833</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>44193</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44151</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44137</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44564</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44252</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44249</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44092</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44608</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44676</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>44110</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44061</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44480</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44375</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>44068</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44063</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44134</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44223</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44081</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44831</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44536</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44468</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44482</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44673</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44705</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>44490</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>44069</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44831</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>44179</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44456</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44295</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44308</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44216</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44106</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44582</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44186</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44126</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44274</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44833</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44172</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44053</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44053</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44053</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44223</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44420</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44375</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44146</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44067</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44203</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44432</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44087</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44062.58306712963</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44223</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44375</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>44624</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44071</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>44182</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44420</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44438</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44794</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44532</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44811</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44075</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44159</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44061</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>44741</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>44053.38900462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44593</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44386</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>44420</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44441</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>44484</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>44188</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>44496</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>44686</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>44714</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44827</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44151</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44068</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>44091</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44655</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44314</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44473</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44614</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>44683</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44532</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44099</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44526</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44713</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44201</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44643</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44263</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44278</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>44071</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>44320</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44426</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44552</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>44712</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44419</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44053.54267361111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44612</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44645</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44434</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45740.5121412037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45153</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45618</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44894</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>44473</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>45406</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45335</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44755</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45216</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44749</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45247</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45194</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45174</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>44893</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>44834</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45048</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45749.84371527778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>44725</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45248</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45156</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45736</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45247</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44447</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45099</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45049</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44794</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44126</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>44113</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44468</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45079</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45168</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45744</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45427</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44901</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45748</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44593</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44151</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45149</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>44053.41018518519</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45420</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45390</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44154</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44732</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22943,7 +22943,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45273</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45280</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45512</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44880</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44928</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>45546.35145833333</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44438</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44862</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45467.48797453703</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45447</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45681.4413425926</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45715</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45016</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45505</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45505</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45229</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45168</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45546.34954861111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>44526</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45744</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44470</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45310</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>44090</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44252</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45218</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45194</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45182</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>44994</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44529</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44068</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45776</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45414</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45085</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45631</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>44592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>44473</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45054</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45538</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44236</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>44516</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45677</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45677</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45252</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45582</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>44966</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45175</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45016</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44530</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44565</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45127</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45566</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45432</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45505</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45026</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45156</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45047</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45238</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45618</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44258</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45505</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45205</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44939</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45324</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45168</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45054</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45341</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45180</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45733.55538194445</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45225</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45063</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45681.43521990741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45194</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44260</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45715</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45800.46510416667</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>44831</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>44876</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>44942</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45660</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44624</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45307</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45132</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44999</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>44995</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>44719</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45175</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>44349</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45238</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45660</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44725</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44826</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45539</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45194</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44218</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45184</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45712.63252314815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45149</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45817.49964120371</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>44827</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44084</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>44373</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45237</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44827</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>44064</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>44063</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45680</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45825</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45054</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45825</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45712.54284722222</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>44300</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45776</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45825</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45390</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45103</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45168</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45168</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>45831.66277777778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44935</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45677</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45216</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45831</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45209</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>45833</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>44215</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45597</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>45729.59356481482</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>44484</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>44651</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>45092</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>44118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>44610</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>44502</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45575</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45153</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>44824</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45355</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>44882</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48559,7 +48559,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45481</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45180</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45152</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45716.63163194444</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45740.50628472222</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49667,7 +49667,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>45637</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45134</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>44827</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45569</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>45013</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44061</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>44551</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>44258</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>44641</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45026</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45400</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>44822</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44083</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>45716.43703703704</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>44490</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2447,7 +2447,7 @@
         <v>44468</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45715</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>44098</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>44235</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2899,7 +2899,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>45385</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         <v>44235</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>44280</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>44278</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>44053</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>44455</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         <v>44295</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>44341</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>45324</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>45016</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45399</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
         <v>45566</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44980</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4913,7 +4913,7 @@
         <v>44942</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45147</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>44319</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>44526</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5954,7 +5954,7 @@
         <v>45595</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45400</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45191</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45239</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7005,7 +7005,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44876</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>45450</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>45328</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44417</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44060</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44229</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44083</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44353</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44337</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44411</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>44449</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8352,7 +8352,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8409,7 +8409,7 @@
         <v>44477</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8466,7 +8466,7 @@
         <v>44564</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44827</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44193</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         <v>44215</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8751,7 +8751,7 @@
         <v>44833</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>44193</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>44151</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         <v>44137</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>44564</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>44252</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>44249</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>44092</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9393,7 +9393,7 @@
         <v>44608</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>44676</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>44110</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44061</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9683,7 +9683,7 @@
         <v>44480</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>44375</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>44068</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44063</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9911,7 +9911,7 @@
         <v>44134</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9968,7 +9968,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44223</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10082,7 +10082,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10201,7 +10201,7 @@
         <v>44081</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44831</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10372,7 +10372,7 @@
         <v>44536</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>44468</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>44482</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10662,7 +10662,7 @@
         <v>44673</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>44705</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>44490</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
         <v>44069</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44831</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11123,7 +11123,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11180,7 +11180,7 @@
         <v>44179</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11237,7 +11237,7 @@
         <v>44456</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>44295</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
         <v>44308</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11470,7 +11470,7 @@
         <v>44216</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>44106</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44582</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44186</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44126</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44274</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44833</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44172</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44053</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44053</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>44053</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12273,7 +12273,7 @@
         <v>44223</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12330,7 +12330,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>44420</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12501,7 +12501,7 @@
         <v>44375</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>44594</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>44594</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>44146</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>44067</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>44203</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>44432</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>44087</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13014,7 +13014,7 @@
         <v>44062.58306712963</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13071,7 +13071,7 @@
         <v>44223</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13128,7 +13128,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44375</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13242,7 +13242,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>44624</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>44071</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>44182</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13470,7 +13470,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44420</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44447</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44438</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44794</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44532</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44811</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44075</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14330,7 +14330,7 @@
         <v>44159</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14387,7 +14387,7 @@
         <v>44061</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14444,7 +14444,7 @@
         <v>44375</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>44741</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14558,7 +14558,7 @@
         <v>44053.38900462963</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>44593</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44386</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>44420</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>44441</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>44484</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15019,7 +15019,7 @@
         <v>44188</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15076,7 +15076,7 @@
         <v>44496</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>44686</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>44714</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44827</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44151</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>44068</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>44091</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15537,7 +15537,7 @@
         <v>44655</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>44314</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44473</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15936,7 +15936,7 @@
         <v>44614</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15993,7 +15993,7 @@
         <v>44683</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16050,7 +16050,7 @@
         <v>44532</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44099</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44526</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>44713</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44201</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>44643</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16563,7 +16563,7 @@
         <v>44263</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16620,7 +16620,7 @@
         <v>44482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44278</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>44071</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>44320</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44426</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>44552</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>44712</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17076,7 +17076,7 @@
         <v>44419</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17133,7 +17133,7 @@
         <v>44053.54267361111</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44612</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44645</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>44434</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>45740.5121412037</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45153</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17656,7 +17656,7 @@
         <v>45618</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44894</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17770,7 +17770,7 @@
         <v>44473</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17827,7 +17827,7 @@
         <v>45406</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17941,7 +17941,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18112,7 +18112,7 @@
         <v>45335</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18226,7 +18226,7 @@
         <v>44755</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18283,7 +18283,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>45216</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18454,7 +18454,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18511,7 +18511,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18568,7 +18568,7 @@
         <v>44749</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18682,7 +18682,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45247</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18915,7 +18915,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45194</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45174</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19205,7 +19205,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>44893</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19443,7 +19443,7 @@
         <v>44834</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45048</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19619,7 +19619,7 @@
         <v>45749.84371527778</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45071</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>44725</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>45248</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19904,7 +19904,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45156</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45736</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20251,7 +20251,7 @@
         <v>45247</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44447</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20370,7 +20370,7 @@
         <v>45099</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20546,7 +20546,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20603,7 +20603,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>45049</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>44794</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20841,7 +20841,7 @@
         <v>44126</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>44113</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>44468</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45079</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
         <v>45168</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>45744</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21193,7 +21193,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21307,7 +21307,7 @@
         <v>45427</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21483,7 +21483,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44901</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45748</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>44593</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21944,7 +21944,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>44151</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22063,7 +22063,7 @@
         <v>45149</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>44053.41018518519</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22358,7 +22358,7 @@
         <v>45420</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45390</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>44154</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22762,7 +22762,7 @@
         <v>44732</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>44439</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22943,7 +22943,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23000,7 +23000,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23181,7 +23181,7 @@
         <v>45273</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23238,7 +23238,7 @@
         <v>45280</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23523,7 +23523,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45512</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23637,7 +23637,7 @@
         <v>44880</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23751,7 +23751,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23808,7 +23808,7 @@
         <v>44928</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23870,7 +23870,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23984,7 +23984,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>45546.35145833333</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44438</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24160,7 +24160,7 @@
         <v>44862</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24222,7 +24222,7 @@
         <v>45467.48797453703</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24403,7 +24403,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24636,7 +24636,7 @@
         <v>45447</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45681.4413425926</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>45715</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>45016</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25268,7 +25268,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45505</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45505</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25439,7 +25439,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25900,7 +25900,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>45229</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26014,7 +26014,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26423,7 +26423,7 @@
         <v>45168</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26485,7 +26485,7 @@
         <v>45546.34954861111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>44526</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>45744</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26656,7 +26656,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26770,7 +26770,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26827,7 +26827,7 @@
         <v>44470</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>45310</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27117,7 +27117,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>44090</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27231,7 +27231,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>44252</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>45218</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27464,7 +27464,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45194</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         <v>45182</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>44994</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27749,7 +27749,7 @@
         <v>44529</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>44068</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45776</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28034,7 +28034,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28148,7 +28148,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         <v>45414</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45085</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28438,7 +28438,7 @@
         <v>45631</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28495,7 +28495,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28552,7 +28552,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>44592</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28666,7 +28666,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28723,7 +28723,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28899,7 +28899,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         <v>44473</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29070,7 +29070,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45054</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29241,7 +29241,7 @@
         <v>45538</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         <v>44236</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29417,7 +29417,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29474,7 +29474,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29531,7 +29531,7 @@
         <v>44516</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29588,7 +29588,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29702,7 +29702,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29759,7 +29759,7 @@
         <v>45677</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29816,7 +29816,7 @@
         <v>45677</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45252</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30106,7 +30106,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>45582</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30225,7 +30225,7 @@
         <v>44966</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30282,7 +30282,7 @@
         <v>45175</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30339,7 +30339,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30396,7 +30396,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30567,7 +30567,7 @@
         <v>45016</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30624,7 +30624,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30800,7 +30800,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30857,7 +30857,7 @@
         <v>44530</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30914,7 +30914,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30971,7 +30971,7 @@
         <v>44565</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -31028,7 +31028,7 @@
         <v>45127</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31085,7 +31085,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31142,7 +31142,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>45566</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31276,7 +31276,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>45432</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>45505</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>45026</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>45156</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31846,7 +31846,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31903,7 +31903,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31960,7 +31960,7 @@
         <v>45047</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -32017,7 +32017,7 @@
         <v>45238</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45618</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32136,7 +32136,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>44258</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32312,7 +32312,7 @@
         <v>45505</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32426,7 +32426,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32483,7 +32483,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32602,7 +32602,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32664,7 +32664,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32788,7 +32788,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45205</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32964,7 +32964,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -33021,7 +33021,7 @@
         <v>44939</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33135,7 +33135,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33192,7 +33192,7 @@
         <v>45324</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>45168</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>45054</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45341</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33668,7 +33668,7 @@
         <v>45180</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45733.55538194445</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33782,7 +33782,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33839,7 +33839,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33896,7 +33896,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33953,7 +33953,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>45225</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45063</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45681.43521990741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45194</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44260</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34714,7 +34714,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34771,7 +34771,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45715</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45800.46510416667</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>44831</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35175,7 +35175,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35232,7 +35232,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35289,7 +35289,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>44876</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35527,7 +35527,7 @@
         <v>44942</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>45660</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>44624</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35760,7 +35760,7 @@
         <v>45638</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45307</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45132</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -36102,7 +36102,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36159,7 +36159,7 @@
         <v>45743</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36273,7 +36273,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36506,7 +36506,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36848,7 +36848,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44999</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37143,7 +37143,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37200,7 +37200,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37723,7 +37723,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>44995</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>44719</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45175</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -38070,7 +38070,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38184,7 +38184,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38298,7 +38298,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38355,7 +38355,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>44349</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38531,7 +38531,7 @@
         <v>45238</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45660</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>44725</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44819</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38992,7 +38992,7 @@
         <v>44826</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -39049,7 +39049,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39106,7 +39106,7 @@
         <v>45539</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39163,7 +39163,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45194</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39339,7 +39339,7 @@
         <v>44218</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45184</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45185</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39795,7 +39795,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39852,7 +39852,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>45712.63252314815</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40313,7 +40313,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45149</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40603,7 +40603,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41131,7 +41131,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41188,7 +41188,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41245,7 +41245,7 @@
         <v>45817.49964120371</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41421,7 +41421,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41602,7 +41602,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41659,7 +41659,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>44827</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41773,7 +41773,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41830,7 +41830,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41887,7 +41887,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44084</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -42063,7 +42063,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42125,7 +42125,7 @@
         <v>44373</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42182,7 +42182,7 @@
         <v>45237</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42239,7 +42239,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>44827</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42410,7 +42410,7 @@
         <v>44064</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42581,7 +42581,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42638,7 +42638,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42695,7 +42695,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42809,7 +42809,7 @@
         <v>44063</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42866,7 +42866,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42980,7 +42980,7 @@
         <v>45680</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -43042,7 +43042,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43099,7 +43099,7 @@
         <v>45825</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45054</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43213,7 +43213,7 @@
         <v>45825</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45712.54284722222</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43389,7 +43389,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>44300</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43503,7 +43503,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43560,7 +43560,7 @@
         <v>45776</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43617,7 +43617,7 @@
         <v>45825</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43674,7 +43674,7 @@
         <v>45390</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43788,7 +43788,7 @@
         <v>45103</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43845,7 +43845,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43902,7 +43902,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45168</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45168</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44757,7 +44757,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44814,7 +44814,7 @@
         <v>45831.66277777778</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>44935</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45677</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45275,7 +45275,7 @@
         <v>45216</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45332,7 +45332,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45389,7 +45389,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45446,7 +45446,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45503,7 +45503,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45617,7 +45617,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45674,7 +45674,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45731,7 +45731,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45788,7 +45788,7 @@
         <v>45831</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45850,7 +45850,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45907,7 +45907,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45964,7 +45964,7 @@
         <v>45209</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -46021,7 +46021,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46192,7 +46192,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46249,7 +46249,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46363,7 +46363,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46420,7 +46420,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46477,7 +46477,7 @@
         <v>45833</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46534,7 +46534,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46591,7 +46591,7 @@
         <v>44215</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46648,7 +46648,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46762,7 +46762,7 @@
         <v>45597</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46824,7 +46824,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46881,7 +46881,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>45729.59356481482</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46995,7 +46995,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47057,7 +47057,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>44484</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47233,7 +47233,7 @@
         <v>44651</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47352,7 +47352,7 @@
         <v>45092</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47409,7 +47409,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47466,7 +47466,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>44118</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47580,7 +47580,7 @@
         <v>44610</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>44502</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45575</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47756,7 +47756,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47813,7 +47813,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47870,7 +47870,7 @@
         <v>45153</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47984,7 +47984,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48041,7 +48041,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48098,7 +48098,7 @@
         <v>44824</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48155,7 +48155,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48212,7 +48212,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48274,7 +48274,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>45355</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48388,7 +48388,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48445,7 +48445,7 @@
         <v>44882</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48559,7 +48559,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45481</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45180</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49196,7 +49196,7 @@
         <v>45152</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45716.63163194444</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49310,7 +49310,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49367,7 +49367,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45740.50628472222</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49667,7 +49667,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49724,7 +49724,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49848,7 +49848,7 @@
         <v>45637</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45134</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>44827</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -50019,7 +50019,7 @@
         <v>45569</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -50076,7 +50076,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -50133,7 +50133,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>45013</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>44641</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45400</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44822</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45026</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44083</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>44235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45716.43703703704</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>44490</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>44559</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45385</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44098</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45715</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>44280</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44278</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44235</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44468</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>44455</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>44295</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44341</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45324</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45399</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44319</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44526</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45191</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>45239</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45147</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45595</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45399</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45400</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44876</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>45450</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>45328</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44417</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>44980</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>45016</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45566</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44942</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44060</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44229</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>44083</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44353</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44337</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44411</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44477</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44449</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44564</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44827</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>44193</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44215</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44833</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44193</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44151</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>44137</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>44564</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44252</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44092</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44608</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44249</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44676</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44110</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44061</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>44375</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>44063</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44068</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44134</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>44480</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44223</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44831</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>44081</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>44536</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44468</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44482</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44673</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>44705</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44490</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>44069</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>44831</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44179</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44456</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>44106</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44295</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44308</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44216</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44582</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44186</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44126</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>44146</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>44833</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44274</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44172</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44223</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44420</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44375</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44594</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44067</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44203</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44432</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44062.58306712963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44087</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44223</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44375</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44624</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44071</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44182</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44420</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44447</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44438</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44811</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44159</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44061</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44593</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44375</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44441</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44386</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44496</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44484</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44420</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44827</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44188</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44686</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44151</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44068</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44091</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>44473</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44655</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44314</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>44614</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44532</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44683</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44099</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44713</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44526</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44482</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44201</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44643</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44263</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44071</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44278</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44552</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44426</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44320</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44612</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44712</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44419</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44434</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>44794</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44532</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>44645</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>44755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44075</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45618</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>45406</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45335</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45216</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44749</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45247</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45744</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45174</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45079</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45744</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45427</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44834</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>44901</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45310</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44252</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45218</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45776</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45194</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45182</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44994</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44529</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44068</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44151</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>44473</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45252</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45582</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>44966</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45420</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>45016</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>44530</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45156</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45618</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45205</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45168</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45054</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45341</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45800.46510416667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44942</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45638</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45743</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45063</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45681.43521990741</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>45512</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>44880</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45194</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44260</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44928</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45715</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44438</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44862</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>44876</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45660</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44624</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45505</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45132</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45539</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45168</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45546.34954861111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44526</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44470</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44090</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>44719</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45175</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45414</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45085</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45631</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44349</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45817.49964120371</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44592</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44725</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>44819</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45054</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44826</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45194</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44218</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>44236</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45712.63252314815</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45677</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45677</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45825</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45825</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45776</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45825</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45175</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44565</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45831.66277777778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45127</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>44827</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45566</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45432</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45505</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>44084</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>45026</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45831</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45237</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45047</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45833</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45054</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45712.54284722222</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45238</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44258</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45505</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45209</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>44939</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>45324</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45180</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44215</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45733.55538194445</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45597</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45225</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>44484</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>44651</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45092</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>44118</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>44610</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44831</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44502</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45575</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45307</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45153</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45355</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>44995</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44882</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45238</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45660</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45481</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45180</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>45184</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45185</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45152</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45716.63163194444</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45149</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45740.50628472222</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45637</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45134</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>44827</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45569</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>44373</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44827</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>44064</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43021,7 +43021,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45013</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>44063</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>45680</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44300</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45390</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45103</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45168</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45168</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>44935</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>44893</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45677</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45216</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45740.5121412037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44725</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>44894</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45156</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>44473</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>45247</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45049</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>44794</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45194</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45048</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45168</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45248</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45736</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>44447</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45099</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>44126</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>45149</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>44113</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>44468</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>44732</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45280</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45748</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>44593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>45546.35145833333</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45390</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>44154</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45447</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>44439</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45681.4413425926</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45273</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45715</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45016</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45505</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44061</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>44224</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>44641</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
         <v>45400</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>44822</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         <v>45026</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>44083</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>44235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>45716.43703703704</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
         <v>44490</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>44559</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45385</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>44098</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>45715</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>44280</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44278</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>44235</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         <v>44468</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>44455</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>44295</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44341</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>45324</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
         <v>45399</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>44319</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4738,7 +4738,7 @@
         <v>44526</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45191</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
         <v>45239</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45147</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>45595</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>45399</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>45400</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44876</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6147,7 +6147,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>45450</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>45328</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         <v>44417</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6767,7 +6767,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6942,7 +6942,7 @@
         <v>44980</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>45016</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45566</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44942</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         <v>44060</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44229</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7863,7 +7863,7 @@
         <v>44083</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7977,7 +7977,7 @@
         <v>44353</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44337</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44411</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>44477</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44449</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         <v>44564</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44827</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>44193</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44215</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         <v>44833</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8718,7 +8718,7 @@
         <v>44193</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>44151</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8837,7 +8837,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8894,7 +8894,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>44137</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9013,7 +9013,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>44564</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         <v>44252</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
         <v>44092</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44608</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44249</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9360,7 +9360,7 @@
         <v>44676</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44110</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         <v>44061</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
         <v>44375</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>44063</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9707,7 +9707,7 @@
         <v>44068</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9764,7 +9764,7 @@
         <v>44134</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>44480</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9935,7 +9935,7 @@
         <v>44223</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9992,7 +9992,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44831</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>44081</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10282,7 +10282,7 @@
         <v>44536</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>44468</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         <v>44482</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44673</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10629,7 +10629,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>44705</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10748,7 +10748,7 @@
         <v>44490</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10805,7 +10805,7 @@
         <v>44375</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>44069</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10976,7 +10976,7 @@
         <v>44831</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11090,7 +11090,7 @@
         <v>44179</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11147,7 +11147,7 @@
         <v>44456</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>44106</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>44295</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44308</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44216</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44582</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>44186</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11727,7 +11727,7 @@
         <v>44126</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11784,7 +11784,7 @@
         <v>44146</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11898,7 +11898,7 @@
         <v>44833</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>44274</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>44172</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>44223</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12126,7 +12126,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44420</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44375</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44594</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44594</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44067</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44203</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44432</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12696,7 +12696,7 @@
         <v>44062.58306712963</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>44087</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>44223</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12867,7 +12867,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>44375</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12981,7 +12981,7 @@
         <v>44624</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13095,7 +13095,7 @@
         <v>44071</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44182</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13323,7 +13323,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>44420</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13499,7 +13499,7 @@
         <v>44447</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13556,7 +13556,7 @@
         <v>44438</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>44811</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13727,7 +13727,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44159</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>44061</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13898,7 +13898,7 @@
         <v>44593</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44375</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>44441</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>44386</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>44496</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14354,7 +14354,7 @@
         <v>44484</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44420</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14468,7 +14468,7 @@
         <v>44827</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14525,7 +14525,7 @@
         <v>44188</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>44686</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14644,7 +14644,7 @@
         <v>44151</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>44714</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>44068</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>44091</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>44473</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14986,7 +14986,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44655</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44314</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>44614</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44532</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>44683</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15499,7 +15499,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15613,7 +15613,7 @@
         <v>44099</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15670,7 +15670,7 @@
         <v>44713</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15727,7 +15727,7 @@
         <v>44526</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44482</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44201</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44643</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44263</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44071</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>44278</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44552</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>44426</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44320</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>44612</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44712</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16644,7 +16644,7 @@
         <v>44419</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>44434</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>44794</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16815,7 +16815,7 @@
         <v>44532</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>44645</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>44755</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44075</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17100,7 +17100,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>45618</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17276,7 +17276,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>45406</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45335</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17618,7 +17618,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45216</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18079,7 +18079,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>44749</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45247</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18374,7 +18374,7 @@
         <v>45744</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45174</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18545,7 +18545,7 @@
         <v>45079</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45744</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45427</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44834</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>44901</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45310</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44252</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45218</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45776</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45194</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>45182</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44994</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44529</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>44068</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>44151</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20446,7 +20446,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>44473</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20736,7 +20736,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>44516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21135,7 +21135,7 @@
         <v>45252</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45582</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21373,7 +21373,7 @@
         <v>44966</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45420</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>45016</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21544,7 +21544,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21720,7 +21720,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>44530</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45156</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45618</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22548,7 +22548,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45205</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22843,7 +22843,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45168</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>45054</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23019,7 +23019,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>45341</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>45800.46510416667</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23418,7 +23418,7 @@
         <v>44942</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45638</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23708,7 +23708,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>45743</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23822,7 +23822,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23936,7 +23936,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24164,7 +24164,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24340,7 +24340,7 @@
         <v>45063</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24397,7 +24397,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24511,7 +24511,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>45681.43521990741</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24687,7 +24687,7 @@
         <v>45512</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24744,7 +24744,7 @@
         <v>44880</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45194</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44260</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>44928</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24982,7 +24982,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25039,7 +25039,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45715</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44438</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>44862</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25396,7 +25396,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25629,7 +25629,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25686,7 +25686,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>44876</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45660</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>44624</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25914,7 +25914,7 @@
         <v>45505</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>45132</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26437,7 +26437,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45539</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45168</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26732,7 +26732,7 @@
         <v>45546.34954861111</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>44526</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>44470</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27245,7 +27245,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>44090</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27649,7 +27649,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27706,7 +27706,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27820,7 +27820,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>44719</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -28048,7 +28048,7 @@
         <v>45175</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>45414</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28395,7 +28395,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28509,7 +28509,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45085</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28680,7 +28680,7 @@
         <v>45631</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28794,7 +28794,7 @@
         <v>44349</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45817.49964120371</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>44592</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29141,7 +29141,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44725</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>44819</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45054</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44826</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45538</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45194</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>44218</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29887,7 +29887,7 @@
         <v>44236</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>45712.63252314815</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45677</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30234,7 +30234,7 @@
         <v>45677</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45825</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45825</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30576,7 +30576,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>45776</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45825</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30923,7 +30923,7 @@
         <v>45175</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30980,7 +30980,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31845,7 +31845,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31902,7 +31902,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32073,7 +32073,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32130,7 +32130,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>44565</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32477,7 +32477,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32534,7 +32534,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32591,7 +32591,7 @@
         <v>45831.66277777778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45127</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32705,7 +32705,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32762,7 +32762,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32886,7 +32886,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32943,7 +32943,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>44827</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33057,7 +33057,7 @@
         <v>45566</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33228,7 +33228,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33285,7 +33285,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>45432</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>45505</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>44084</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>45026</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45831</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33751,7 +33751,7 @@
         <v>45237</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33808,7 +33808,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>45047</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34150,7 +34150,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34207,7 +34207,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45833</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45054</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45712.54284722222</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45238</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>44258</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45505</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45209</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>44939</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36108,7 +36108,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36165,7 +36165,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36222,7 +36222,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>45324</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45180</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>44215</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45733.55538194445</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45597</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36931,7 +36931,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36988,7 +36988,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37045,7 +37045,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37159,7 +37159,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37216,7 +37216,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37278,7 +37278,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37335,7 +37335,7 @@
         <v>45225</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>44484</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37630,7 +37630,7 @@
         <v>44651</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45092</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37863,7 +37863,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37920,7 +37920,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37977,7 +37977,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>44118</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38091,7 +38091,7 @@
         <v>44610</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38267,7 +38267,7 @@
         <v>44831</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38386,7 +38386,7 @@
         <v>44502</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38443,7 +38443,7 @@
         <v>45575</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38500,7 +38500,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38619,7 +38619,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38676,7 +38676,7 @@
         <v>45307</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38790,7 +38790,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38847,7 +38847,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38904,7 +38904,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38961,7 +38961,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45153</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39075,7 +39075,7 @@
         <v>44999</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39132,7 +39132,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39189,7 +39189,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39246,7 +39246,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39417,7 +39417,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39536,7 +39536,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39593,7 +39593,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39712,7 +39712,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39883,7 +39883,7 @@
         <v>45355</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>44995</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39997,7 +39997,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40054,7 +40054,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40111,7 +40111,7 @@
         <v>44882</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40168,7 +40168,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40225,7 +40225,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40344,7 +40344,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40401,7 +40401,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40458,7 +40458,7 @@
         <v>45238</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40520,7 +40520,7 @@
         <v>45660</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40634,7 +40634,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40691,7 +40691,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40748,7 +40748,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40805,7 +40805,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40862,7 +40862,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41033,7 +41033,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41090,7 +41090,7 @@
         <v>45481</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41147,7 +41147,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>45180</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>45184</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41328,7 +41328,7 @@
         <v>45185</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>45152</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41499,7 +41499,7 @@
         <v>45716.63163194444</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41727,7 +41727,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41851,7 +41851,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>45149</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>45740.50628472222</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42151,7 +42151,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42332,7 +42332,7 @@
         <v>45637</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>45134</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42446,7 +42446,7 @@
         <v>44827</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42565,7 +42565,7 @@
         <v>45569</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>44373</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>44827</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>44064</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -43021,7 +43021,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45013</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>44063</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>45680</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>45153</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43425,7 +43425,7 @@
         <v>44300</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43482,7 +43482,7 @@
         <v>45390</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45103</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43710,7 +43710,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43767,7 +43767,7 @@
         <v>45168</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45168</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44223,7 +44223,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44285,7 +44285,7 @@
         <v>44935</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44342,7 +44342,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44399,7 +44399,7 @@
         <v>44893</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45677</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45216</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45740.5121412037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44689,7 +44689,7 @@
         <v>44725</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44746,7 +44746,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>44894</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>45156</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44917,7 +44917,7 @@
         <v>44473</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44974,7 +44974,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -45031,7 +45031,7 @@
         <v>45247</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45326,7 +45326,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45049</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>44794</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45497,7 +45497,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45554,7 +45554,7 @@
         <v>45194</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45673,7 +45673,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45048</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45792,7 +45792,7 @@
         <v>45071</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>45168</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45906,7 +45906,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45963,7 +45963,7 @@
         <v>45248</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -46020,7 +46020,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46134,7 +46134,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46191,7 +46191,7 @@
         <v>45736</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46248,7 +46248,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46367,7 +46367,7 @@
         <v>44447</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46429,7 +46429,7 @@
         <v>45099</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46548,7 +46548,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46605,7 +46605,7 @@
         <v>44126</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46662,7 +46662,7 @@
         <v>45149</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46776,7 +46776,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46833,7 +46833,7 @@
         <v>44113</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>44468</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46957,7 +46957,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -47019,7 +47019,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47076,7 +47076,7 @@
         <v>44732</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47138,7 +47138,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47200,7 +47200,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47257,7 +47257,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47319,7 +47319,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47376,7 +47376,7 @@
         <v>45280</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47433,7 +47433,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47490,7 +47490,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47604,7 +47604,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47661,7 +47661,7 @@
         <v>45748</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47718,7 +47718,7 @@
         <v>44593</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47775,7 +47775,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47832,7 +47832,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47889,7 +47889,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47946,7 +47946,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -48003,7 +48003,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48060,7 +48060,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48117,7 +48117,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48179,7 +48179,7 @@
         <v>45546.35145833333</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48241,7 +48241,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45390</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48536,7 +48536,7 @@
         <v>44154</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48593,7 +48593,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48764,7 +48764,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48826,7 +48826,7 @@
         <v>45447</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48883,7 +48883,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>44439</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48997,7 +48997,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45681.4413425926</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -49116,7 +49116,7 @@
         <v>45273</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45715</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49230,7 +49230,7 @@
         <v>45016</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49344,7 +49344,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49401,7 +49401,7 @@
         <v>45505</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49458,7 +49458,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49572,7 +49572,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>45229</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49800,7 +49800,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45026</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>44822</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>45400</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44083</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44235</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44490</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44468</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>44280</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44278</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44559</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44098</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45716.43703703704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44235</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45385</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44455</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44295</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44341</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45328</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45016</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45450</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44319</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45191</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45239</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44980</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45595</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44876</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44417</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45147</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44942</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>44526</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45400</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45399</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45324</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45566</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44229</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44083</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44353</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44337</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44411</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44477</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44449</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44564</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44827</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44193</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44215</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>44833</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44193</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44137</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44151</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44564</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>44252</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44092</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44249</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>44110</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>44676</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>44375</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>44068</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44134</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44480</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44223</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44081</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44831</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44536</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>44482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44468</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44673</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44490</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44375</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44069</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44831</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>44179</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>44456</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44106</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44295</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44308</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44216</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44582</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44186</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44126</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44146</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44833</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44274</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44172</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44223</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44420</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44375</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44594</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44594</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44067</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44203</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44087</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44375</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44624</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44071</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44182</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44420</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44447</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44438</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>44811</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>44794</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>44532</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44075</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44159</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>44375</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44741</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44593</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44386</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>44420</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44484</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44441</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>44188</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>44496</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>44714</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44151</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>44827</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44068</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44314</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>44091</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44473</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>44655</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>44614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44532</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44099</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44526</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>44683</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44201</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>44643</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44278</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>44263</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>44320</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44712</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44426</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44419</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44482</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44645</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44071</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45736</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44612</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45538</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>44552</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44434</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45273</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44794</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45168</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44893</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45063</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44258</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45597</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>44966</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45153</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44755</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45071</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45132</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45156</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44862</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44565</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44236</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45247</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44438</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44530</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45054</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45618</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44252</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44651</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45127</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45238</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45744</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45744</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44610</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45355</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45427</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>45180</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45618</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>44113</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45153</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44725</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45566</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>44473</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>44928</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45180</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45229</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45680</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44827</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45085</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45776</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45310</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45194</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45637</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45103</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45184</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45512</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>44473</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>44935</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45677</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>44154</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45414</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45149</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45149</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45054</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45175</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>44118</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44349</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45194</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>44126</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45307</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>44894</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45016</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>45194</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44719</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45237</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45712.63252314815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45216</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44592</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44831</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44827</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44502</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45677</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>44827</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45660</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45390</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44593</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44942</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45341</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45660</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45638</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45218</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45168</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45743</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45225</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45048</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>44151</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>44901</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>44090</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45324</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45539</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44447</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45175</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>44484</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>44068</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45156</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>45013</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45047</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>44218</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>44373</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45216</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45631</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>45817.49964120371</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45677</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45168</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>44526</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45079</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45194</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>45238</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>44439</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45205</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45825</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45280</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45420</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45825</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45825</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>44468</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>44749</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>44826</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45776</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45390</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45481</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>45174</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45748</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>44834</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45831.66277777778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45831</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45715</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45209</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45582</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45447</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>44876</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45833</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45049</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>44084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>44994</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>44939</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>44529</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>45681.43521990741</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45168</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44882</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>45715</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45099</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>44516</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44819</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45252</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45575</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>45182</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45134</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>44260</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>45247</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>44624</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>44215</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45016</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>45569</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>45406</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>44999</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45505</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>44995</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45335</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45505</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45505</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45888</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45168</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44725</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>45026</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45248</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45092</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44732</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>44300</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45054</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         <v>45505</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45026</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>44822</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         <v>45400</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44083</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44235</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44490</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44468</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>44280</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44278</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44559</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44098</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45716.43703703704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
         <v>44235</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>45385</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         <v>44455</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>44295</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>44341</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45328</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4215,7 +4215,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>45016</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4474,7 +4474,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45450</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>44319</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         <v>45191</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4920,7 +4920,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>45239</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         <v>44980</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45595</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>44876</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5892,7 +5892,7 @@
         <v>44417</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>45147</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44942</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45399</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v>44526</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>45400</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6839,7 +6839,7 @@
         <v>45399</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>45324</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>45566</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7570,7 +7570,7 @@
         <v>44229</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44083</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7684,7 +7684,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>44353</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>44337</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>44411</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7969,7 +7969,7 @@
         <v>44477</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8026,7 +8026,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8083,7 +8083,7 @@
         <v>44449</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>44564</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>44827</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>44193</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         <v>44215</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8425,7 +8425,7 @@
         <v>44833</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44193</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8601,7 +8601,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>44137</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44151</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>44564</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8891,7 +8891,7 @@
         <v>44252</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44092</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44249</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
         <v>44110</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>44676</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9300,7 +9300,7 @@
         <v>44375</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>44068</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9414,7 +9414,7 @@
         <v>44134</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
         <v>44480</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9585,7 +9585,7 @@
         <v>44223</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9761,7 +9761,7 @@
         <v>44081</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44831</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>44536</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10046,7 +10046,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10103,7 +10103,7 @@
         <v>44482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10160,7 +10160,7 @@
         <v>44468</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44673</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44705</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44490</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44375</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44069</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>44831</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10683,7 +10683,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>44179</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>44456</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>44106</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>44295</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44308</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44216</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44582</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44186</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44126</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44146</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44833</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44274</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44172</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44223</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11833,7 +11833,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>44420</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>44375</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44594</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>44594</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12118,7 +12118,7 @@
         <v>44067</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12232,7 +12232,7 @@
         <v>44203</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44087</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44223</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44375</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44624</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44071</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44182</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44420</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44447</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13149,7 +13149,7 @@
         <v>44438</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13263,7 +13263,7 @@
         <v>44811</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>44794</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>44532</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13491,7 +13491,7 @@
         <v>44075</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>44159</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>44375</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>44741</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>44593</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13947,7 +13947,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14004,7 +14004,7 @@
         <v>44386</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14061,7 +14061,7 @@
         <v>44420</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14118,7 +14118,7 @@
         <v>44484</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>44441</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14232,7 +14232,7 @@
         <v>44188</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>44496</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14346,7 +14346,7 @@
         <v>44714</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>44686</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14465,7 +14465,7 @@
         <v>44151</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>44827</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>44068</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>44314</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>44091</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14807,7 +14807,7 @@
         <v>44473</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>44655</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14921,7 +14921,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15092,7 +15092,7 @@
         <v>44614</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15149,7 +15149,7 @@
         <v>44532</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>44099</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15320,7 +15320,7 @@
         <v>44713</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44526</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15548,7 +15548,7 @@
         <v>44683</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15605,7 +15605,7 @@
         <v>44201</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>44643</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44278</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>44263</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>44320</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15947,7 +15947,7 @@
         <v>44712</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>44426</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16118,7 +16118,7 @@
         <v>44419</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16175,7 +16175,7 @@
         <v>44482</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44645</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44071</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>45736</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>44612</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45538</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16693,7 +16693,7 @@
         <v>44552</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16750,7 +16750,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44434</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>45273</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44794</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45168</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17149,7 +17149,7 @@
         <v>44893</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>45063</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17268,7 +17268,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17325,7 +17325,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17382,7 +17382,7 @@
         <v>44258</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>45597</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>44966</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17558,7 +17558,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>45153</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17734,7 +17734,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44755</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17848,7 +17848,7 @@
         <v>45071</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17905,7 +17905,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45132</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>45156</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18076,7 +18076,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18133,7 +18133,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18252,7 +18252,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18366,7 +18366,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44862</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>44565</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>44236</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18951,7 +18951,7 @@
         <v>45247</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19008,7 +19008,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44438</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>44530</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19412,7 +19412,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19469,7 +19469,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45054</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45618</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19878,7 +19878,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20049,7 +20049,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44252</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20173,7 +20173,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>44651</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>44470</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45127</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20815,7 +20815,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20872,7 +20872,7 @@
         <v>45238</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45744</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>45744</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44610</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21628,7 +21628,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21685,7 +21685,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>45355</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22322,7 +22322,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22379,7 +22379,7 @@
         <v>45427</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22436,7 +22436,7 @@
         <v>45180</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22498,7 +22498,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>45618</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22850,7 +22850,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>44113</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>45153</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44725</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23088,7 +23088,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45566</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>44473</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23549,7 +23549,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23663,7 +23663,7 @@
         <v>44928</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23839,7 +23839,7 @@
         <v>45180</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23896,7 +23896,7 @@
         <v>45229</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45680</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>44827</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24647,7 +24647,7 @@
         <v>45085</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24761,7 +24761,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24818,7 +24818,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24875,7 +24875,7 @@
         <v>45776</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>45310</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25103,7 +25103,7 @@
         <v>45194</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25160,7 +25160,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25217,7 +25217,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25274,7 +25274,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25502,7 +25502,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25559,7 +25559,7 @@
         <v>45637</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25616,7 +25616,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45103</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45184</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26310,7 +26310,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45512</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26771,7 +26771,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26828,7 +26828,7 @@
         <v>44473</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26885,7 +26885,7 @@
         <v>45432</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27113,7 +27113,7 @@
         <v>44935</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45677</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27284,7 +27284,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>44154</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27626,7 +27626,7 @@
         <v>45414</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27683,7 +27683,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27859,7 +27859,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45149</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45149</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28112,7 +28112,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28169,7 +28169,7 @@
         <v>45054</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28226,7 +28226,7 @@
         <v>45175</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28283,7 +28283,7 @@
         <v>44118</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44349</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28459,7 +28459,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28521,7 +28521,7 @@
         <v>45185</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28578,7 +28578,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45194</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28697,7 +28697,7 @@
         <v>44126</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28754,7 +28754,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28811,7 +28811,7 @@
         <v>45307</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28925,7 +28925,7 @@
         <v>44894</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>45016</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29153,7 +29153,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29324,7 +29324,7 @@
         <v>45194</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>44719</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29552,7 +29552,7 @@
         <v>45237</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>45712.63252314815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45216</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29723,7 +29723,7 @@
         <v>44592</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29837,7 +29837,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -30013,7 +30013,7 @@
         <v>44831</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30070,7 +30070,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         <v>44827</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30308,7 +30308,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>44502</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30479,7 +30479,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45677</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30593,7 +30593,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30764,7 +30764,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30935,7 +30935,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30992,7 +30992,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31049,7 +31049,7 @@
         <v>44827</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31106,7 +31106,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31163,7 +31163,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31220,7 +31220,7 @@
         <v>45660</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31277,7 +31277,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31458,7 +31458,7 @@
         <v>45390</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>44593</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31572,7 +31572,7 @@
         <v>44942</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31629,7 +31629,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31743,7 +31743,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31800,7 +31800,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45341</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31971,7 +31971,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32033,7 +32033,7 @@
         <v>45660</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>45638</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45218</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32204,7 +32204,7 @@
         <v>45168</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32375,7 +32375,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45743</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32717,7 +32717,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32774,7 +32774,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32831,7 +32831,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>45225</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -33002,7 +33002,7 @@
         <v>45048</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33059,7 +33059,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33121,7 +33121,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33178,7 +33178,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>44151</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33354,7 +33354,7 @@
         <v>44901</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>44090</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45324</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33850,7 +33850,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33964,7 +33964,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -34021,7 +34021,7 @@
         <v>45539</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34135,7 +34135,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34192,7 +34192,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44447</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34311,7 +34311,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34368,7 +34368,7 @@
         <v>45175</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34482,7 +34482,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34544,7 +34544,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34601,7 +34601,7 @@
         <v>44484</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34663,7 +34663,7 @@
         <v>44068</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45156</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34834,7 +34834,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35295,7 +35295,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35352,7 +35352,7 @@
         <v>45013</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>45047</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35766,7 +35766,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>44218</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35937,7 +35937,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35999,7 +35999,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -36056,7 +36056,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36113,7 +36113,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36170,7 +36170,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36284,7 +36284,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36341,7 +36341,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36455,7 +36455,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>44373</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36745,7 +36745,7 @@
         <v>45216</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>45631</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36916,7 +36916,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36973,7 +36973,7 @@
         <v>45817.49964120371</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>45677</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>45168</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>44526</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37263,7 +37263,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37320,7 +37320,7 @@
         <v>45079</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37558,7 +37558,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37615,7 +37615,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37729,7 +37729,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37786,7 +37786,7 @@
         <v>45194</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37843,7 +37843,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37900,7 +37900,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38133,7 +38133,7 @@
         <v>45238</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38195,7 +38195,7 @@
         <v>44439</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38252,7 +38252,7 @@
         <v>45205</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38366,7 +38366,7 @@
         <v>45825</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38423,7 +38423,7 @@
         <v>45280</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>45420</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38537,7 +38537,7 @@
         <v>45825</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38594,7 +38594,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38656,7 +38656,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45825</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>44468</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38894,7 +38894,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>44749</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>44826</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39065,7 +39065,7 @@
         <v>45776</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39179,7 +39179,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39236,7 +39236,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>45390</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39350,7 +39350,7 @@
         <v>44824</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39407,7 +39407,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>45481</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39692,7 +39692,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39749,7 +39749,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39868,7 +39868,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39925,7 +39925,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40158,7 +40158,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40215,7 +40215,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40339,7 +40339,7 @@
         <v>45174</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40396,7 +40396,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40510,7 +40510,7 @@
         <v>45748</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40624,7 +40624,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40681,7 +40681,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>44880</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40852,7 +40852,7 @@
         <v>44834</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45831.66277777778</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45831</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41085,7 +41085,7 @@
         <v>45715</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45209</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45582</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45447</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>44876</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41888,7 +41888,7 @@
         <v>45833</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>45049</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -42002,7 +42002,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>44084</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42116,7 +42116,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42173,7 +42173,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42230,7 +42230,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42287,7 +42287,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42344,7 +42344,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>44994</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42458,7 +42458,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>44939</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42629,7 +42629,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>44529</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42743,7 +42743,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42800,7 +42800,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42857,7 +42857,7 @@
         <v>45681.43521990741</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42914,7 +42914,7 @@
         <v>45168</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42971,7 +42971,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43028,7 +43028,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43085,7 +43085,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>44882</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43199,7 +43199,7 @@
         <v>45715</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45099</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>44516</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43427,7 +43427,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44819</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45252</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43774,7 +43774,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43836,7 +43836,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>45575</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43950,7 +43950,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -44007,7 +44007,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44064,7 +44064,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44178,7 +44178,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44235,7 +44235,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44354,7 +44354,7 @@
         <v>45182</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44411,7 +44411,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44473,7 +44473,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44530,7 +44530,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44587,7 +44587,7 @@
         <v>45134</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44644,7 +44644,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44701,7 +44701,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45152</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44929,7 +44929,7 @@
         <v>44260</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>45247</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>44624</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>44215</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>45016</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>45569</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>45406</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45390,7 +45390,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45509,7 +45509,7 @@
         <v>44999</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45566,7 +45566,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45623,7 +45623,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45680,7 +45680,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45737,7 +45737,7 @@
         <v>45505</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45851,7 +45851,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46493,7 +46493,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46555,7 +46555,7 @@
         <v>44995</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46612,7 +46612,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46669,7 +46669,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46726,7 +46726,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46783,7 +46783,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46840,7 +46840,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46959,7 +46959,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45335</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47073,7 +47073,7 @@
         <v>45505</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47130,7 +47130,7 @@
         <v>45505</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45888</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47249,7 +47249,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47306,7 +47306,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47420,7 +47420,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47477,7 +47477,7 @@
         <v>45168</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47596,7 +47596,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47653,7 +47653,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47715,7 +47715,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47777,7 +47777,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47834,7 +47834,7 @@
         <v>44725</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47891,7 +47891,7 @@
         <v>45026</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47948,7 +47948,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48005,7 +48005,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48062,7 +48062,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48119,7 +48119,7 @@
         <v>45248</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>45092</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48233,7 +48233,7 @@
         <v>44732</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48295,7 +48295,7 @@
         <v>44300</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48352,7 +48352,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48409,7 +48409,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>45054</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48818,7 +48818,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         <v>45505</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45400</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>44822</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45026</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44083</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44490</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>44098</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44559</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45385</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44235</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44280</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>44278</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44468</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44455</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44295</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>45324</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45399</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44319</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44526</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45147</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45595</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45399</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45400</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45191</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45239</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44876</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>45016</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45450</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45566</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45328</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44942</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44417</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44980</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>44229</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44083</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44353</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44337</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44449</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44477</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44564</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44827</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44193</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44833</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44215</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44193</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44137</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44252</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>44092</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>44249</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>44608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>44676</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>44110</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44480</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44375</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44134</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44223</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44081</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44831</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44536</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44468</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44482</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44673</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44490</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44375</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>44831</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44179</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44456</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44295</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44106</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44308</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44216</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44582</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44186</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44126</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44146</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44833</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44274</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>44172</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>44223</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44420</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44375</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44594</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44594</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44203</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>44087</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44223</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44375</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44624</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44182</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44420</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44447</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>44438</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>44811</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>44075</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44159</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44593</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44375</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44741</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>44441</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>44386</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>44496</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44420</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>44827</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44484</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>44188</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44686</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>44714</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44473</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>44614</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>44532</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44314</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44683</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44091</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>44655</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>44099</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44713</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44526</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44482</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44643</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44263</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44201</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44278</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>44552</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44426</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44320</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>44612</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44712</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44419</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44434</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44794</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45174</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44532</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44645</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44755</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>44834</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45618</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45406</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45335</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45216</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44749</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45247</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45744</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45079</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45744</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45776</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45427</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45310</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>44901</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44252</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45218</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45194</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45182</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44994</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44151</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44529</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45420</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45512</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>44880</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44928</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44473</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>44438</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44862</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>44516</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45252</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45505</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45582</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44966</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45016</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>44530</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45156</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45168</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44526</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44470</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45618</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>44090</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45414</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45205</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45085</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45631</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44942</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45054</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45638</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45743</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44592</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45341</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45054</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45538</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44236</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45677</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45677</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45063</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45539</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45175</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>44260</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45715</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44565</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45127</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45566</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>45505</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44876</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45026</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45660</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45047</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45132</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45238</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44258</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45505</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45825</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45825</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44939</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45324</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45825</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45180</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>45225</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45831</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45175</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44349</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>44725</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44819</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44826</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45833</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44831</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45194</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44218</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>45307</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44999</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44827</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44084</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45237</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44995</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45888</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45238</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45660</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45054</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45894.65247685185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45184</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45895.51850694444</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45209</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45149</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>44215</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44373</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45597</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44827</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45680</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>44300</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45390</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45103</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>44484</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45168</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45168</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>44651</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44935</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45677</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45216</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44894</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44473</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44118</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44610</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45194</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44502</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45575</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45048</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>45071</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45248</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45153</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>45736</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44447</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>44824</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>44126</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>44113</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44468</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45355</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45748</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44593</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44882</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45390</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44154</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44439</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45273</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45481</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45180</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45152</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45637</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45134</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         <v>44827</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45569</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45013</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45153</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>44893</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44725</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45247</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45049</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>44794</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45168</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>45149</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>44732</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45280</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46888,7 +46888,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47173,7 +47173,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>45447</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45715</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45016</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45505</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45400</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>44822</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45026</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44083</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44490</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44235</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>44098</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>44559</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2800,7 +2800,7 @@
         <v>45385</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>44235</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         <v>44280</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>44278</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44468</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44455</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44295</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>45324</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45399</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>44319</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
         <v>44526</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45147</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>45595</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5165,7 +5165,7 @@
         <v>45399</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>45400</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>45191</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>45239</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5867,7 +5867,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44876</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         <v>45016</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6404,7 +6404,7 @@
         <v>45450</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>45566</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>45328</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>44942</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>44417</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44980</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7275,7 +7275,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>44229</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         <v>44083</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         <v>44353</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44337</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         <v>44411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>44449</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>44477</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         <v>44564</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>44827</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>44193</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44833</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>44215</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8391,7 +8391,7 @@
         <v>44193</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         <v>44151</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44137</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8686,7 +8686,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         <v>44564</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>44252</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         <v>44092</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>44249</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>44608</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>44676</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9147,7 +9147,7 @@
         <v>44110</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>44480</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44375</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44134</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>44223</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>44081</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>44831</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44536</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44468</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10017,7 +10017,7 @@
         <v>44482</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44673</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10193,7 +10193,7 @@
         <v>44705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>44490</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>44375</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>44831</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44179</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44456</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44295</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>44106</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44308</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10830,7 +10830,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44216</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10944,7 +10944,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11001,7 +11001,7 @@
         <v>44582</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11115,7 +11115,7 @@
         <v>44186</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44126</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>44146</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44833</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44274</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>44172</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11514,7 +11514,7 @@
         <v>44223</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44420</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>44375</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11799,7 +11799,7 @@
         <v>44594</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44594</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44203</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>44432</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>44087</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12198,7 +12198,7 @@
         <v>44223</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>44375</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>44624</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>44182</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12483,7 +12483,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12597,7 +12597,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12659,7 +12659,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12716,7 +12716,7 @@
         <v>44420</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12773,7 +12773,7 @@
         <v>44447</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12830,7 +12830,7 @@
         <v>44438</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>44811</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13058,7 +13058,7 @@
         <v>44075</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44159</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44593</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>44375</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13400,7 +13400,7 @@
         <v>44741</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>44441</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13571,7 +13571,7 @@
         <v>44386</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>44496</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13685,7 +13685,7 @@
         <v>44420</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
         <v>44827</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13799,7 +13799,7 @@
         <v>44484</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13856,7 +13856,7 @@
         <v>44188</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>44686</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>44151</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>44714</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44473</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14203,7 +14203,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14317,7 +14317,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>44614</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>44532</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14545,7 +14545,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44314</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>44683</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>44091</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
         <v>44655</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14887,7 +14887,7 @@
         <v>44099</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>44713</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15001,7 +15001,7 @@
         <v>44526</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44482</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15172,7 +15172,7 @@
         <v>44643</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15229,7 +15229,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44263</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>44201</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>44278</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>44552</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15514,7 +15514,7 @@
         <v>44426</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44320</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>44612</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44712</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44419</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>44434</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44794</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45174</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44532</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44645</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44755</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>44834</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16550,7 +16550,7 @@
         <v>45618</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>45406</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>45335</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17073,7 +17073,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>45216</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17301,7 +17301,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>44749</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45247</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17591,7 +17591,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45744</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17705,7 +17705,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45079</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45744</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45776</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45427</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18570,7 +18570,7 @@
         <v>45310</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>44901</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>44252</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18808,7 +18808,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45218</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18922,7 +18922,7 @@
         <v>45194</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45182</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>44994</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>44151</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19269,7 +19269,7 @@
         <v>44529</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45420</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19497,7 +19497,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19611,7 +19611,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19668,7 +19668,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45512</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20015,7 +20015,7 @@
         <v>44880</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>44928</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44473</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>44438</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>44862</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20424,7 +20424,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20538,7 +20538,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>44516</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20709,7 +20709,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20823,7 +20823,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20900,7 +20900,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21071,7 +21071,7 @@
         <v>45252</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21247,7 +21247,7 @@
         <v>45505</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21304,7 +21304,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45582</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>44966</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21480,7 +21480,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45016</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21656,7 +21656,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>44530</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21941,7 +21941,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22055,7 +22055,7 @@
         <v>45156</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45607.52395833333</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45168</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>44526</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44470</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45618</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>44090</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22868,7 +22868,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23111,7 +23111,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23225,7 +23225,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23287,7 +23287,7 @@
         <v>45414</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45205</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45085</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45631</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>44942</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45168</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>45054</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>45638</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24375,7 +24375,7 @@
         <v>45743</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44592</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>45341</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24893,7 +24893,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25012,7 +25012,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25069,7 +25069,7 @@
         <v>45054</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45538</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>44236</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>45677</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45677</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25473,7 +25473,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25530,7 +25530,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25587,7 +25587,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25649,7 +25649,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25820,7 +25820,7 @@
         <v>45063</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45539</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45194</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45175</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26281,7 +26281,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>44260</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26514,7 +26514,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26742,7 +26742,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26799,7 +26799,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>45715</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27089,7 +27089,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45813.45128472222</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>44565</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27431,7 +27431,7 @@
         <v>45127</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27550,7 +27550,7 @@
         <v>45566</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27721,7 +27721,7 @@
         <v>45432</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>45505</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>44876</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>45026</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28006,7 +28006,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>45660</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28120,7 +28120,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>45047</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45132</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>45238</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>44258</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28581,7 +28581,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45505</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28871,7 +28871,7 @@
         <v>45821.6225462963</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45821.61653935185</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29042,7 +29042,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29104,7 +29104,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29161,7 +29161,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45825</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45825</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>44939</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45324</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29585,7 +29585,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29642,7 +29642,7 @@
         <v>45776</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29699,7 +29699,7 @@
         <v>45825</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29756,7 +29756,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29875,7 +29875,7 @@
         <v>45180</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30103,7 +30103,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30160,7 +30160,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30217,7 +30217,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30274,7 +30274,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30559,7 +30559,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30673,7 +30673,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30730,7 +30730,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30787,7 +30787,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30844,7 +30844,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>45225</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31015,7 +31015,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31072,7 +31072,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31134,7 +31134,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31191,7 +31191,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>45831</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31310,7 +31310,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31372,7 +31372,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31429,7 +31429,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>44719</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45175</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31657,7 +31657,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31714,7 +31714,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31828,7 +31828,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31942,7 +31942,7 @@
         <v>44349</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32004,7 +32004,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>44725</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>44819</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44826</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32460,7 +32460,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32517,7 +32517,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32574,7 +32574,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>45833</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44831</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32802,7 +32802,7 @@
         <v>45194</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32859,7 +32859,7 @@
         <v>44218</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32916,7 +32916,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33035,7 +33035,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33092,7 +33092,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33211,7 +33211,7 @@
         <v>45307</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33496,7 +33496,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33553,7 +33553,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33610,7 +33610,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33672,7 +33672,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33729,7 +33729,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33843,7 +33843,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33900,7 +33900,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34014,7 +34014,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34071,7 +34071,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34371,7 +34371,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34547,7 +34547,7 @@
         <v>44999</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34666,7 +34666,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34723,7 +34723,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34842,7 +34842,7 @@
         <v>44827</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34899,7 +34899,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34956,7 +34956,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35246,7 +35246,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35303,7 +35303,7 @@
         <v>44084</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35360,7 +35360,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35474,7 +35474,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
         <v>45237</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35588,7 +35588,7 @@
         <v>44995</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35702,7 +35702,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35816,7 +35816,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35873,7 +35873,7 @@
         <v>45888</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>45238</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36054,7 +36054,7 @@
         <v>45660</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36168,7 +36168,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36339,7 +36339,7 @@
         <v>45054</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36453,7 +36453,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36510,7 +36510,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36572,7 +36572,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36634,7 +36634,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36691,7 +36691,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36748,7 +36748,7 @@
         <v>45894.65247685185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45184</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36862,7 +36862,7 @@
         <v>45185</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36919,7 +36919,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36976,7 +36976,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37033,7 +37033,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37261,7 +37261,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45895.51850694444</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37375,7 +37375,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37432,7 +37432,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37494,7 +37494,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37608,7 +37608,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37665,7 +37665,7 @@
         <v>45209</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37779,7 +37779,7 @@
         <v>45149</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37836,7 +37836,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37893,7 +37893,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37955,7 +37955,7 @@
         <v>44215</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38069,7 +38069,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38131,7 +38131,7 @@
         <v>44373</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45597</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38307,7 +38307,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38364,7 +38364,7 @@
         <v>44827</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38535,7 +38535,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38592,7 +38592,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38706,7 +38706,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38763,7 +38763,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38825,7 +38825,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38882,7 +38882,7 @@
         <v>45680</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>44300</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -39001,7 +39001,7 @@
         <v>45390</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39058,7 +39058,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39115,7 +39115,7 @@
         <v>45103</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>44484</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39234,7 +39234,7 @@
         <v>45168</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39291,7 +39291,7 @@
         <v>45168</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>44651</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39576,7 +39576,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39633,7 +39633,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39695,7 +39695,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39757,7 +39757,7 @@
         <v>44935</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39871,7 +39871,7 @@
         <v>45677</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39928,7 +39928,7 @@
         <v>45216</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>45092</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40042,7 +40042,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40099,7 +40099,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40213,7 +40213,7 @@
         <v>44894</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44473</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44118</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>44610</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40565,7 +40565,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45194</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44502</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45575</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40912,7 +40912,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45048</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41145,7 +41145,7 @@
         <v>45071</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41202,7 +41202,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45248</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>45153</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>45736</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41601,7 +41601,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44447</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41720,7 +41720,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41839,7 +41839,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>44824</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42010,7 +42010,7 @@
         <v>44126</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>44113</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>44468</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42191,7 +42191,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42310,7 +42310,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42367,7 +42367,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45355</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42538,7 +42538,7 @@
         <v>45748</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>44593</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42652,7 +42652,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42709,7 +42709,7 @@
         <v>44882</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42766,7 +42766,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42823,7 +42823,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42880,7 +42880,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42942,7 +42942,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42999,7 +42999,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43056,7 +43056,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43113,7 +43113,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43175,7 +43175,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43232,7 +43232,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>45390</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43346,7 +43346,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43460,7 +43460,7 @@
         <v>44154</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43517,7 +43517,7 @@
         <v>44439</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43574,7 +43574,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43631,7 +43631,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>45273</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>45481</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>45180</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43978,7 +43978,7 @@
         <v>45152</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44035,7 +44035,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44263,7 +44263,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44325,7 +44325,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44387,7 +44387,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>45637</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>45134</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         <v>44827</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>45569</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45013</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45153</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45257,7 +45257,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45314,7 +45314,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>44893</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44725</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45547,7 +45547,7 @@
         <v>45156</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45604,7 +45604,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45661,7 +45661,7 @@
         <v>45247</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45049</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>44794</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>45168</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46008,7 +46008,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46065,7 +46065,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46241,7 +46241,7 @@
         <v>45149</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46298,7 +46298,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46355,7 +46355,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>44732</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>45280</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46831,7 +46831,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46888,7 +46888,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47173,7 +47173,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47530,7 +47530,7 @@
         <v>45447</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47706,7 +47706,7 @@
         <v>45715</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47763,7 +47763,7 @@
         <v>45016</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47820,7 +47820,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47877,7 +47877,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47934,7 +47934,7 @@
         <v>45505</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45229</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44822</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45400</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45026</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44083</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44235</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44490</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44468</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>44280</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44278</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44559</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
         <v>44098</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>44235</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>45385</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>44455</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>44295</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3674,7 +3674,7 @@
         <v>44341</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>45016</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45624.29501157408</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>45239</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>44980</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45595</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5001,7 +5001,7 @@
         <v>44876</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         <v>44417</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45147</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5520,7 +5520,7 @@
         <v>44942</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5605,7 +5605,7 @@
         <v>45399</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>45904.5654050926</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44526</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5953,7 +5953,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>45400</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45399</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6297,7 +6297,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45324</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>45566</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>45328</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>45191</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7267,7 +7267,7 @@
         <v>45450</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44319</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
         <v>44229</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>44083</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44337</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         <v>44411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44353</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44449</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>44477</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         <v>44564</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>44827</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>44215</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44193</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>44833</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44193</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44151</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44137</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44564</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>44092</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44252</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>44249</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44608</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44110</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         <v>44480</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44676</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44375</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44134</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44223</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44831</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>44081</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44536</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44468</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44482</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10221,7 +10221,7 @@
         <v>44705</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>44673</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>44490</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44375</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44831</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44179</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44456</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44106</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44308</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44295</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10972,7 +10972,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>44216</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>44582</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>44186</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11200,7 +11200,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>44126</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>44146</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>44274</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>44833</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>44172</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11599,7 +11599,7 @@
         <v>44223</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>44420</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44375</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>44594</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44594</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11998,7 +11998,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44203</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12112,7 +12112,7 @@
         <v>44432</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12169,7 +12169,7 @@
         <v>44087</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44223</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44624</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44182</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>44420</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         <v>44447</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44438</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12915,7 +12915,7 @@
         <v>44811</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44159</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13086,7 +13086,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13143,7 +13143,7 @@
         <v>44375</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>44593</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44741</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13428,7 +13428,7 @@
         <v>44386</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>44420</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13542,7 +13542,7 @@
         <v>44441</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13599,7 +13599,7 @@
         <v>44188</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44827</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>44496</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>44484</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44714</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13884,7 +13884,7 @@
         <v>44686</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13946,7 +13946,7 @@
         <v>44151</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14117,7 +14117,7 @@
         <v>44473</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>44683</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>44614</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>44532</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14573,7 +14573,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>44091</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14687,7 +14687,7 @@
         <v>44655</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14744,7 +14744,7 @@
         <v>44713</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14801,7 +14801,7 @@
         <v>44314</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14858,7 +14858,7 @@
         <v>44099</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>44201</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>44526</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>44643</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>44278</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>44263</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>44320</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>44426</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>44482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>44712</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>44419</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>44552</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>44612</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44645</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>44434</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>44794</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16003,7 +16003,7 @@
         <v>44532</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>44755</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45736</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>44651</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45127</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44794</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>45153</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45229</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44827</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45744</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17443,7 +17443,7 @@
         <v>45063</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45597</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45776</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>45180</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>44610</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18080,7 +18080,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18137,7 +18137,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18370,7 +18370,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18603,7 +18603,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45355</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45132</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>45180</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45618</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19981,7 +19981,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20100,7 +20100,7 @@
         <v>44236</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45103</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>45566</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>44473</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20581,7 +20581,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20638,7 +20638,7 @@
         <v>45680</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20700,7 +20700,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20757,7 +20757,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45085</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>45310</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>45194</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>44154</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45637</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21684,7 +21684,7 @@
         <v>45149</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21741,7 +21741,7 @@
         <v>45149</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21798,7 +21798,7 @@
         <v>45054</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45175</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>44118</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45184</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>44349</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22259,7 +22259,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22435,7 +22435,7 @@
         <v>45185</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45194</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22549,7 +22549,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45307</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22663,7 +22663,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>45512</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>44473</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45432</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45016</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45194</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>44719</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44942</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>44935</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>45677</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>45237</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>45414</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>44592</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45638</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>45546.47163194444</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24378,7 +24378,7 @@
         <v>44831</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24435,7 +24435,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45743</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24896,7 +24896,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>44502</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45677</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25466,7 +25466,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25585,7 +25585,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>44126</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>44894</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25932,7 +25932,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45390</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26170,7 +26170,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26227,7 +26227,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45216</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>45660</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45168</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45625.57662037037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45225</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27030,7 +27030,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27087,7 +27087,7 @@
         <v>45810.45333333333</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44827</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45539</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45048</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>44151</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>44901</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27895,7 +27895,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>44827</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -28009,7 +28009,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         <v>45660</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28242,7 +28242,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>45813.48049768519</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>45156</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29159,7 +29159,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29221,7 +29221,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>44593</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29449,7 +29449,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29563,7 +29563,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29620,7 +29620,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29677,7 +29677,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29734,7 +29734,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45341</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29848,7 +29848,7 @@
         <v>45218</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29905,7 +29905,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29962,7 +29962,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30143,7 +30143,7 @@
         <v>45825</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45631</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30314,7 +30314,7 @@
         <v>45825</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30371,7 +30371,7 @@
         <v>45825</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30428,7 +30428,7 @@
         <v>45776</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30485,7 +30485,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30542,7 +30542,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30599,7 +30599,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>45827.44266203704</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30770,7 +30770,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30884,7 +30884,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31055,7 +31055,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31169,7 +31169,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31226,7 +31226,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31283,7 +31283,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31397,7 +31397,7 @@
         <v>45831</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31573,7 +31573,7 @@
         <v>44090</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31692,7 +31692,7 @@
         <v>45324</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45833</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45833.32751157408</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31997,7 +31997,7 @@
         <v>45168</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32054,7 +32054,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>45834.53628472222</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32339,7 +32339,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32401,7 +32401,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32463,7 +32463,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32577,7 +32577,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32634,7 +32634,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32691,7 +32691,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>44447</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>45175</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32981,7 +32981,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33038,7 +33038,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33095,7 +33095,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33214,7 +33214,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33271,7 +33271,7 @@
         <v>44484</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33675,7 +33675,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33732,7 +33732,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33794,7 +33794,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45888</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34089,7 +34089,7 @@
         <v>45194</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45894.65247685185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34550,7 +34550,7 @@
         <v>45895.51850694444</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>45238</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34669,7 +34669,7 @@
         <v>45013</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45901.66907407407</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45901.66547453704</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>45901</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>45903.67501157407</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44375</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>45902.32299768519</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>45205</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>45047</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45280</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>45420</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>45903.70535879629</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45903.49077546296</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>44218</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35705,7 +35705,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35762,7 +35762,7 @@
         <v>45905.43545138889</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35819,7 +35819,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35995,7 +35995,7 @@
         <v>44373</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>45216</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36166,7 +36166,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36228,7 +36228,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>45174</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45730.33155092593</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36528,7 +36528,7 @@
         <v>45677</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>44526</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36699,7 +36699,7 @@
         <v>44880</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36756,7 +36756,7 @@
         <v>45729.59702546296</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45079</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36870,7 +36870,7 @@
         <v>45447</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37155,7 +37155,7 @@
         <v>44876</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37212,7 +37212,7 @@
         <v>45049</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>44084</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37326,7 +37326,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37383,7 +37383,7 @@
         <v>44994</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37440,7 +37440,7 @@
         <v>44439</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37497,7 +37497,7 @@
         <v>44529</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37554,7 +37554,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37611,7 +37611,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37668,7 +37668,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37844,7 +37844,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>44468</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45715</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -38025,7 +38025,7 @@
         <v>44749</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>44826</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>45099</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38253,7 +38253,7 @@
         <v>44516</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38310,7 +38310,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38367,7 +38367,7 @@
         <v>45390</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>44824</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38481,7 +38481,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38538,7 +38538,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38595,7 +38595,7 @@
         <v>45481</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38652,7 +38652,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>45748</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>44834</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38828,7 +38828,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>45715</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38942,7 +38942,7 @@
         <v>45209</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>45582</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39294,7 +39294,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39351,7 +39351,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39408,7 +39408,7 @@
         <v>44939</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39465,7 +39465,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39522,7 +39522,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45168</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39636,7 +39636,7 @@
         <v>45182</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39755,7 +39755,7 @@
         <v>44882</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>45134</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39869,7 +39869,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39926,7 +39926,7 @@
         <v>44819</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39983,7 +39983,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>45152</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40097,7 +40097,7 @@
         <v>45252</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40159,7 +40159,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40273,7 +40273,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>44260</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40449,7 +40449,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45575</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40568,7 +40568,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40625,7 +40625,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45016</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40739,7 +40739,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45569</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40853,7 +40853,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40910,7 +40910,7 @@
         <v>45406</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40967,7 +40967,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41024,7 +41024,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41081,7 +41081,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41314,7 +41314,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41433,7 +41433,7 @@
         <v>45247</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41490,7 +41490,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41547,7 +41547,7 @@
         <v>45505</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41604,7 +41604,7 @@
         <v>44215</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41718,7 +41718,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>44999</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41894,7 +41894,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41951,7 +41951,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45505</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>45168</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42184,7 +42184,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42303,7 +42303,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42365,7 +42365,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42422,7 +42422,7 @@
         <v>44725</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42541,7 +42541,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>44995</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42717,7 +42717,7 @@
         <v>45335</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>45505</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42888,7 +42888,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42945,7 +42945,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45092</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43121,7 +43121,7 @@
         <v>44732</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>44300</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43240,7 +43240,7 @@
         <v>45026</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43354,7 +43354,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43649,7 +43649,7 @@
         <v>45273</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43706,7 +43706,7 @@
         <v>45168</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43763,7 +43763,7 @@
         <v>44893</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43882,7 +43882,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43939,7 +43939,7 @@
         <v>44258</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
         <v>45071</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44053,7 +44053,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44110,7 +44110,7 @@
         <v>45248</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44167,7 +44167,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44281,7 +44281,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44338,7 +44338,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>45054</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44509,7 +44509,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44566,7 +44566,7 @@
         <v>44862</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44628,7 +44628,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44690,7 +44690,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44747,7 +44747,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45247</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44861,7 +44861,7 @@
         <v>44438</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44918,7 +44918,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>45505</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44530</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>45538</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45203,7 +45203,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45260,7 +45260,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45317,7 +45317,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45374,7 +45374,7 @@
         <v>45618</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45431,7 +45431,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45545,7 +45545,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45602,7 +45602,7 @@
         <v>44966</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45659,7 +45659,7 @@
         <v>45153</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45778,7 +45778,7 @@
         <v>44252</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>45156</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45897,7 +45897,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45959,7 +45959,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46078,7 +46078,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>44565</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45054</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45630.35104166667</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46839,7 +46839,7 @@
         <v>45630.35287037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -47020,7 +47020,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47077,7 +47077,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47134,7 +47134,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47191,7 +47191,7 @@
         <v>44470</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47248,7 +47248,7 @@
         <v>45427</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47362,7 +47362,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47424,7 +47424,7 @@
         <v>45238</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47486,7 +47486,7 @@
         <v>45744</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>45630.41625</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47662,7 +47662,7 @@
         <v>44113</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>44725</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47838,7 +47838,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47895,7 +47895,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -48071,7 +48071,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>44928</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48190,7 +48190,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48247,7 +48247,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48304,7 +48304,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48361,7 +48361,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48418,7 +48418,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48475,7 +48475,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45400</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>44822</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45026</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44490</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44235</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44098</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44559</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45385</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>44235</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44468</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44280</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44278</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44455</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>44295</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44341</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45324</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45399</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44319</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44526</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45147</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45191</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45239</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45595</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>45399</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45400</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>45016</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45566</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44942</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44876</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45328</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>45904.5654050926</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44417</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44980</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44229</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44353</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44337</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44477</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>44449</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44564</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44827</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44215</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44193</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44151</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44137</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44193</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44564</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44252</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44092</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44608</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44249</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>44676</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44110</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44480</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44375</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44134</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44223</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>44831</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44536</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44468</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44482</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44673</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44705</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44375</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>44490</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44831</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44179</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44456</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44295</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44106</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44308</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44216</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44582</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44186</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>44126</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44146</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44833</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44274</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44172</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44223</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44420</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44375</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44594</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44594</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44203</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>44432</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44223</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44087</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44182</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44420</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44447</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44438</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44811</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44593</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44441</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44496</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44484</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44827</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44714</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44375</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44386</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44420</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44473</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44188</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44614</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44532</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44683</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44686</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>44151</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44713</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44201</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44278</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44320</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44712</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44419</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44552</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44645</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45174</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44834</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45618</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>44755</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45406</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45335</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45216</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44314</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44749</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45247</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45079</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45744</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45744</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45427</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44099</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44901</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45776</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45310</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>44151</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44252</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45218</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45194</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45182</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45420</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>44994</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44529</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>44526</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45512</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44880</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>44473</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>44928</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>44516</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44263</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45252</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>44438</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>44862</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45582</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>44966</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45016</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44530</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45505</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44426</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45156</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44612</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45168</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44434</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44526</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44470</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>44090</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45205</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>44794</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45168</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45054</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45341</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44532</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45414</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45085</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45631</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44942</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45638</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45743</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44592</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45063</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45054</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45194</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44260</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>45538</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45715</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44236</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45677</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>44876</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45660</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45175</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45132</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45539</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44565</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45127</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45566</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45432</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45505</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45026</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45047</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45238</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44258</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45505</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44719</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45175</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44349</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>44725</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>44819</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45825</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44939</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45825</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45324</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45776</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45825</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44826</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>45194</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44218</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45180</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45831</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45225</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45833</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44831</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32399,7 +32399,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44827</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45307</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45237</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>44999</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45054</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>44995</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45238</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>45660</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45184</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45149</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44373</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45209</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>44827</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>45680</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>44300</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45390</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45103</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45168</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45168</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>44935</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45677</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45216</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44894</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44473</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45194</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45048</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45071</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45248</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44215</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45736</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44447</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45099</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44126</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44113</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>44468</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45597</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44484</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45390</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>44154</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44439</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45273</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>44651</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44118</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44610</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45894.65247685185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>44502</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45575</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45895.51850694444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45153</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>44824</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45901.66907407407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45902.32299768519</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45901.66547453704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45355</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44375</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>44882</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45903.49077546296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45903.67501157407</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45903.70535879629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>44655</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45481</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>45888</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45905.43545138889</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45152</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>44091</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45909.55575231482</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45909.54364583334</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45909.56019675926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45910.45300925926</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45618</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45909.54929398148</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45841</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45905</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45905</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45908</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45908</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45908</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45908</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45908</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45911.45987268518</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45912.65081018519</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>45637</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45134</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45841</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45841</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>44827</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>45569</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45013</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45153</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>44893</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>44725</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45156</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45247</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45049</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>44794</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45168</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45149</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44732</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46720,7 +46720,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45280</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47362,7 +47362,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45447</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45715</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45016</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45505</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45400</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
         <v>44822</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45026</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44490</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44235</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44098</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>44559</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45385</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         <v>44235</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>44468</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>44280</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>44278</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>44455</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>44295</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44341</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45324</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>45399</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44319</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>44526</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4739,7 +4739,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4824,7 +4824,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>45147</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>45191</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5088,7 +5088,7 @@
         <v>45239</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         <v>45595</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>45399</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>45400</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>45016</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45566</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6223,7 +6223,7 @@
         <v>44942</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6393,7 +6393,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6478,7 +6478,7 @@
         <v>44876</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>45450</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6657,7 +6657,7 @@
         <v>45328</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>45904.5654050926</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44417</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7010,7 +7010,7 @@
         <v>44980</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7095,7 +7095,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         <v>44229</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>44353</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>44337</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>44477</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7730,7 +7730,7 @@
         <v>44411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7844,7 +7844,7 @@
         <v>44449</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44564</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44827</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8072,7 +8072,7 @@
         <v>44215</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>44193</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44833</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44151</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44137</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44193</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
         <v>44564</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8595,7 +8595,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44252</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44092</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>44608</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44249</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         <v>44676</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44110</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>44480</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44375</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44134</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44223</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
         <v>44831</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44536</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9693,7 +9693,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44468</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9812,7 +9812,7 @@
         <v>44482</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>44673</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44705</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10045,7 +10045,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>44375</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>44490</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
         <v>44831</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44179</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44456</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44295</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44106</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>44308</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>44216</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44582</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44186</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>44126</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11024,7 +11024,7 @@
         <v>44146</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44833</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11195,7 +11195,7 @@
         <v>44274</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44172</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>44223</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11480,7 +11480,7 @@
         <v>44420</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11537,7 +11537,7 @@
         <v>44375</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>44594</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11651,7 +11651,7 @@
         <v>44594</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11708,7 +11708,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>44203</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>44432</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11879,7 +11879,7 @@
         <v>44223</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11993,7 +11993,7 @@
         <v>44087</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44182</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12107,7 +12107,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>44420</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>44447</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>44438</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>44811</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12796,7 +12796,7 @@
         <v>44593</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>44441</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12967,7 +12967,7 @@
         <v>44496</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>44484</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13081,7 +13081,7 @@
         <v>44827</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>44714</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>44375</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13252,7 +13252,7 @@
         <v>44741</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44386</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44420</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44473</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44188</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44614</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44532</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44683</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44686</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>44151</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>44097.5883912037</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44713</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44201</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44278</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>44482</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>44320</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44712</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44419</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44552</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44645</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>45174</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44834</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45618</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         <v>44755</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45406</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15371,7 +15371,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45335</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45216</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>44314</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44749</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16179,7 +16179,7 @@
         <v>45247</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45079</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45744</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45744</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16759,7 +16759,7 @@
         <v>45427</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>44099</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>44901</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17163,7 +17163,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>45776</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45310</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>44151</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>44252</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45218</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         <v>45194</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18033,7 +18033,7 @@
         <v>45182</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45420</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>44994</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44529</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>44526</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18375,7 +18375,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18432,7 +18432,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18489,7 +18489,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18546,7 +18546,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18665,7 +18665,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18950,7 +18950,7 @@
         <v>45512</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44880</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         <v>44473</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>44928</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19468,7 +19468,7 @@
         <v>44516</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>44643</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44263</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19867,7 +19867,7 @@
         <v>45252</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>44438</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>44862</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20105,7 +20105,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45582</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>44966</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20338,7 +20338,7 @@
         <v>45016</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20457,7 +20457,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44530</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45505</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>44426</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45156</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44612</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21337,7 +21337,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21394,7 +21394,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21570,7 +21570,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21689,7 +21689,7 @@
         <v>45168</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21751,7 +21751,7 @@
         <v>44434</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21808,7 +21808,7 @@
         <v>44526</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21865,7 +21865,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44470</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>44090</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45205</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>44794</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22507,7 +22507,7 @@
         <v>45168</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22564,7 +22564,7 @@
         <v>45054</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22621,7 +22621,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22735,7 +22735,7 @@
         <v>45341</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22849,7 +22849,7 @@
         <v>44532</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23020,7 +23020,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23082,7 +23082,7 @@
         <v>45414</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>45085</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45631</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44942</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23481,7 +23481,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23600,7 +23600,7 @@
         <v>45638</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23714,7 +23714,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45743</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>44592</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24056,7 +24056,7 @@
         <v>45063</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24289,7 +24289,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24470,7 +24470,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24584,7 +24584,7 @@
         <v>45054</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45194</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>44260</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>45538</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24879,7 +24879,7 @@
         <v>45715</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>44236</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24998,7 +24998,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45677</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25350,7 +25350,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25407,7 +25407,7 @@
         <v>44876</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45660</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25578,7 +25578,7 @@
         <v>45175</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25749,7 +25749,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25806,7 +25806,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25863,7 +25863,7 @@
         <v>45132</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25920,7 +25920,7 @@
         <v>45539</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26210,7 +26210,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>44565</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45127</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45566</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45432</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45505</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -27013,7 +27013,7 @@
         <v>45026</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>45047</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27526,7 +27526,7 @@
         <v>45238</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>44258</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>45505</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27816,7 +27816,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27992,7 +27992,7 @@
         <v>44719</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45175</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28396,7 +28396,7 @@
         <v>44349</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28458,7 +28458,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28515,7 +28515,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>44725</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28629,7 +28629,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>44819</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>45825</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44939</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28919,7 +28919,7 @@
         <v>45825</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29090,7 +29090,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45324</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29224,7 +29224,7 @@
         <v>45776</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         <v>45825</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29338,7 +29338,7 @@
         <v>44826</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29395,7 +29395,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29680,7 +29680,7 @@
         <v>45194</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29737,7 +29737,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29794,7 +29794,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>44218</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>45180</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30022,7 +30022,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>45832.66162037037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45831</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30597,7 +30597,7 @@
         <v>45225</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30654,7 +30654,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30949,7 +30949,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31063,7 +31063,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>45833</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31762,7 +31762,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>45835.44440972222</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31876,7 +31876,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31933,7 +31933,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32047,7 +32047,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>44831</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32280,7 +32280,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32399,7 +32399,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32461,7 +32461,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32518,7 +32518,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>44827</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32808,7 +32808,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32870,7 +32870,7 @@
         <v>45307</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>45237</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>44999</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33445,7 +33445,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33616,7 +33616,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45054</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>44995</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45238</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34077,7 +34077,7 @@
         <v>45660</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34134,7 +34134,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34305,7 +34305,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>45184</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34481,7 +34481,7 @@
         <v>45185</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34885,7 +34885,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34942,7 +34942,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45149</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35522,7 +35522,7 @@
         <v>44373</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35579,7 +35579,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45209</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>44827</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35864,7 +35864,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>45680</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36097,7 +36097,7 @@
         <v>44300</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>45390</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45103</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36382,7 +36382,7 @@
         <v>45168</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45168</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36667,7 +36667,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>44935</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45677</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45216</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>44894</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>44473</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37304,7 +37304,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37361,7 +37361,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37418,7 +37418,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45194</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37532,7 +37532,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>45048</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37713,7 +37713,7 @@
         <v>45071</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37827,7 +37827,7 @@
         <v>45248</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>44215</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37998,7 +37998,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>45736</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>44447</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38174,7 +38174,7 @@
         <v>45099</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38231,7 +38231,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>44126</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44113</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38526,7 +38526,7 @@
         <v>44468</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45597</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38997,7 +38997,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39054,7 +39054,7 @@
         <v>44593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39111,7 +39111,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39282,7 +39282,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39344,7 +39344,7 @@
         <v>44484</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39463,7 +39463,7 @@
         <v>45390</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39520,7 +39520,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>44154</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39634,7 +39634,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44439</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39805,7 +39805,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>45273</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39919,7 +39919,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39976,7 +39976,7 @@
         <v>44651</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40033,7 +40033,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45092</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40266,7 +40266,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40323,7 +40323,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40437,7 +40437,7 @@
         <v>44118</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40494,7 +40494,7 @@
         <v>44610</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>45894.65247685185</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>44502</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40670,7 +40670,7 @@
         <v>45575</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40784,7 +40784,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40841,7 +40841,7 @@
         <v>45895.51850694444</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40898,7 +40898,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40955,7 +40955,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41012,7 +41012,7 @@
         <v>45153</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>44824</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41416,7 +41416,7 @@
         <v>45901.66907407407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41473,7 +41473,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41530,7 +41530,7 @@
         <v>45902.32299768519</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>45901.66547453704</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45901</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45355</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44375</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>44882</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45903.49077546296</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45903.67501157407</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>45903.70535879629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>44655</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45481</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42903,7 +42903,7 @@
         <v>45888</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45180</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45905.43545138889</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45152</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>44091</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43198,7 +43198,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45909.55575231482</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45909.54364583334</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43369,7 +43369,7 @@
         <v>45909.56019675926</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45910.45300925926</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45618</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45909.54929398148</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43959,7 +43959,7 @@
         <v>45841</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44016,7 +44016,7 @@
         <v>45905</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44073,7 +44073,7 @@
         <v>45905</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45908</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45908</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45908</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45908</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>45908</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45911.45987268518</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45912.65081018519</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44648,7 +44648,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
         <v>45637</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44767,7 +44767,7 @@
         <v>45134</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45908</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>45841</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44995,7 +44995,7 @@
         <v>45841</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45052,7 +45052,7 @@
         <v>44827</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>45569</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45223,7 +45223,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45013</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45153</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45508,7 +45508,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45565,7 +45565,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45622,7 +45622,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45679,7 +45679,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45736,7 +45736,7 @@
         <v>44893</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>44725</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45855,7 +45855,7 @@
         <v>45156</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45912,7 +45912,7 @@
         <v>45247</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45969,7 +45969,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46026,7 +46026,7 @@
         <v>45049</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46083,7 +46083,7 @@
         <v>44794</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46140,7 +46140,7 @@
         <v>45168</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46197,7 +46197,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46254,7 +46254,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>45149</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46425,7 +46425,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46482,7 +46482,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46601,7 +46601,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>44732</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46720,7 +46720,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46844,7 +46844,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46901,7 +46901,7 @@
         <v>45280</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47015,7 +47015,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47072,7 +47072,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47129,7 +47129,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47186,7 +47186,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47243,7 +47243,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47362,7 +47362,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47419,7 +47419,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47533,7 +47533,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47595,7 +47595,7 @@
         <v>45447</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45715</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>45016</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45505</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>45229</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45399</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44551</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>44258</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>44822</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45400</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>45026</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44235</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>44280</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>44490</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>44468</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>44278</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2977,7 +2977,7 @@
         <v>44235</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45385</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44455</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>44295</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>44341</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45016</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45239</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3939,7 +3939,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         <v>44876</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>44980</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>45566.4780787037</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4463,7 +4463,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45595</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44417</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4910,7 +4910,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>45147</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>44942</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>45399</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>44526</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5602,7 +5602,7 @@
         <v>45400</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>45399</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5776,7 +5776,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>45324</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>45566</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6384,7 +6384,7 @@
         <v>45328</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>45904.5654050926</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>45917.35021990741</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>45191</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7086,7 +7086,7 @@
         <v>45450</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>44319</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>44229</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7497,7 +7497,7 @@
         <v>44353</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44337</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44411</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7725,7 +7725,7 @@
         <v>44477</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44449</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7896,7 +7896,7 @@
         <v>44564</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>44827</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8067,7 +8067,7 @@
         <v>44193</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8124,7 +8124,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>44215</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44193</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8357,7 +8357,7 @@
         <v>44151</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>44137</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8533,7 +8533,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>44564</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44252</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         <v>44608</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>44249</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44676</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
         <v>44110</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44480</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>44134</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>44375</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>44223</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44831</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44536</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44468</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
         <v>44482</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9807,7 +9807,7 @@
         <v>44673</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>44705</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9983,7 +9983,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10040,7 +10040,7 @@
         <v>44490</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>44375</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10154,7 +10154,7 @@
         <v>44831</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>44179</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44456</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10382,7 +10382,7 @@
         <v>44295</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44106</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10506,7 +10506,7 @@
         <v>44308</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10563,7 +10563,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44216</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44582</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>44186</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>44126</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         <v>44146</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44274</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>44833</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11190,7 +11190,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44172</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>44223</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>44420</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11475,7 +11475,7 @@
         <v>44594</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>44594</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         <v>44375</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>44203</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>44432</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         <v>44223</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11874,7 +11874,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>44182</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12278,7 +12278,7 @@
         <v>44420</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
         <v>44447</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44438</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>44811</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12620,7 +12620,7 @@
         <v>44375</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44593</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44741</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>44386</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12962,7 +12962,7 @@
         <v>44420</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44441</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13076,7 +13076,7 @@
         <v>44827</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>44188</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13190,7 +13190,7 @@
         <v>44496</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13247,7 +13247,7 @@
         <v>44686</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13309,7 +13309,7 @@
         <v>44151</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13423,7 +13423,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44473</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13765,7 +13765,7 @@
         <v>44614</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>44532</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>44683</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13936,7 +13936,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>44314</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>44713</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
         <v>44482</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>44526</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14335,7 +14335,7 @@
         <v>44643</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44263</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>44552</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>44426</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>44612</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>44434</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14796,7 +14796,7 @@
         <v>44794</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14853,7 +14853,7 @@
         <v>44532</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14910,7 +14910,7 @@
         <v>44755</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14967,7 +14967,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
         <v>44484</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44609.71230324074</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15138,7 +15138,7 @@
         <v>45566.4808449074</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>45229</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>44827</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15480,7 +15480,7 @@
         <v>45723.44018518519</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15542,7 +15542,7 @@
         <v>44236</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45776</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15661,7 +15661,7 @@
         <v>45363.47704861111</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15718,7 +15718,7 @@
         <v>45706.50239583333</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45153</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45315.42144675926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15889,7 +15889,7 @@
         <v>45628.72706018519</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>45695.56203703704</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45695.5696875</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>44958.45609953703</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>44958.45834490741</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45197.40341435185</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>44651</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>45352.49944444445</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16355,7 +16355,7 @@
         <v>45180</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45771.58767361111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16469,7 +16469,7 @@
         <v>45735.35653935185</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>45127</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45783.43402777778</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>44970.31702546297</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>45008.48836805556</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45744</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45278.50741898148</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45268.57443287037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44928.49331018519</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>45742.63379629629</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45302.27971064814</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>45610.65568287037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>45628.73400462963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17386,7 +17386,7 @@
         <v>44610</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>45743.36407407407</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>45743.38579861111</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45691.36315972222</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17681,7 +17681,7 @@
         <v>44530.35085648148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17738,7 +17738,7 @@
         <v>45352.51495370371</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>45566.48396990741</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>45566.48729166666</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>45103</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>44960.49487268519</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45355</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>44992.63921296296</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>45789.49431712963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45714.66180555556</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44963.33652777778</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45180</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44740.59510416666</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45727.37675925926</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45618</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45790.45359953704</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45685.52724537037</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45239.30261574074</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18918,7 +18918,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45566</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19032,7 +19032,7 @@
         <v>44473</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45335.48046296297</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>44154</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>44201</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>44896.59528935186</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45680</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45741.47209490741</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45741.47322916667</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>45149</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>45748.61495370371</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19674,7 +19674,7 @@
         <v>45149</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45054</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>45175</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19845,7 +19845,7 @@
         <v>44118</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45188.538125</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>44278</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45573.46162037037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>44320</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>44349</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45085</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45185</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45194</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45310</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45307</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45594.44086805556</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>44712</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>44419</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45016</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20933,7 +20933,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20990,7 +20990,7 @@
         <v>45194</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>44719</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45237</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21161,7 +21161,7 @@
         <v>45194</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21218,7 +21218,7 @@
         <v>44592</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45191.34582175926</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>44831</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>44732.66290509259</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21446,7 +21446,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45637</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45726.48642361111</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21622,7 +21622,7 @@
         <v>45726.61862268519</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45726.62087962963</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>44502</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21793,7 +21793,7 @@
         <v>44645</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45677</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21907,7 +21907,7 @@
         <v>45511.45795138889</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45715.48555555556</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22021,7 +22021,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22249,7 +22249,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22306,7 +22306,7 @@
         <v>44951.89928240741</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>45184</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22420,7 +22420,7 @@
         <v>44942</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>45370.3781712963</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45399.44796296296</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>45730.33476851852</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45735.35633101852</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22710,7 +22710,7 @@
         <v>45729.47229166667</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45729.481875</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22829,7 +22829,7 @@
         <v>45390</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22886,7 +22886,7 @@
         <v>45799.41569444445</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>45638</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>44889.47004629629</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23062,7 +23062,7 @@
         <v>45649.56431712963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23119,7 +23119,7 @@
         <v>45743</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45321.48475694445</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23233,7 +23233,7 @@
         <v>45637.58633101852</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23290,7 +23290,7 @@
         <v>45800.50819444445</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23347,7 +23347,7 @@
         <v>45660</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>45539.61945601852</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23461,7 +23461,7 @@
         <v>45803.44508101852</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45803.44677083333</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>45736</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23632,7 +23632,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>44811.44258101852</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23746,7 +23746,7 @@
         <v>45168</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23803,7 +23803,7 @@
         <v>45512</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>44949.44762731482</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23917,7 +23917,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23974,7 +23974,7 @@
         <v>44519.98293981481</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>44473</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45432</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45376.49780092593</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45225</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>44935</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45677</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24487,7 +24487,7 @@
         <v>45103.64168981482</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24544,7 +24544,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>45624.42489583333</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45804.36096064815</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24720,7 +24720,7 @@
         <v>45414</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>45048</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24834,7 +24834,7 @@
         <v>45805.41023148148</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24891,7 +24891,7 @@
         <v>45271.88459490741</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24948,7 +24948,7 @@
         <v>45259.3803125</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>44151</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>44901</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45810.44914351852</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25181,7 +25181,7 @@
         <v>45539</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45810.45978009259</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45604.64454861111</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>45266.36511574074</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45622.35957175926</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>44126</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25533,7 +25533,7 @@
         <v>45442.48394675926</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25590,7 +25590,7 @@
         <v>44894</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45719.30990740741</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45693.56089120371</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45810.579375</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25823,7 +25823,7 @@
         <v>45378.62289351852</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>45546.67261574074</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45813.45608796296</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45813.45994212963</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>45812.57268518519</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26165,7 +26165,7 @@
         <v>45812.57512731481</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>45216</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45813.51774305556</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26336,7 +26336,7 @@
         <v>45467.48708333333</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26393,7 +26393,7 @@
         <v>45742.52042824074</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26450,7 +26450,7 @@
         <v>45812.5667824074</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26507,7 +26507,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45812.57081018519</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45156</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26740,7 +26740,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26916,7 +26916,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>45715.64194444445</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>45715.64390046296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>44827</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>45754.62439814815</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>44794</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -27263,7 +27263,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45455.53951388889</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45569.49569444444</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45063</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -27491,7 +27491,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45681.59012731481</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>44827</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45735.63356481482</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45819.56673611111</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>45818.50829861111</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27833,7 +27833,7 @@
         <v>45817.8397337963</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45155.60460648148</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27947,7 +27947,7 @@
         <v>45660</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -28004,7 +28004,7 @@
         <v>45616.46331018519</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -28066,7 +28066,7 @@
         <v>45597</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45690.4284375</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -28190,7 +28190,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45537.59931712963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -28304,7 +28304,7 @@
         <v>45132</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -28361,7 +28361,7 @@
         <v>44593</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -28418,7 +28418,7 @@
         <v>45442.46103009259</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45477.44527777778</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45146.34890046297</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28589,7 +28589,7 @@
         <v>45631</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28646,7 +28646,7 @@
         <v>44526.36217592593</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>45168</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45341</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>44126.6755787037</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>45218</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -29045,7 +29045,7 @@
         <v>45104.52766203704</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -29102,7 +29102,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -29226,7 +29226,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -29283,7 +29283,7 @@
         <v>45532.65594907408</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>45194</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -29459,7 +29459,7 @@
         <v>45726.75759259259</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>45324</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>45656.40385416667</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>45713.37621527778</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45723.43553240741</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29784,7 +29784,7 @@
         <v>45169.62482638889</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44447</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45086.64048611111</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>45175</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45238</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -30079,7 +30079,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45723.44528935185</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -30198,7 +30198,7 @@
         <v>44484</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>45008.45369212963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -30374,7 +30374,7 @@
         <v>45205</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -30431,7 +30431,7 @@
         <v>45034.31502314815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>45280</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45047.82030092592</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30602,7 +30602,7 @@
         <v>45420</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30716,7 +30716,7 @@
         <v>45013</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30892,7 +30892,7 @@
         <v>44818.62078703703</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30954,7 +30954,7 @@
         <v>45047</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45824.46417824074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>44218</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>45715.49478009259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -31296,7 +31296,7 @@
         <v>45825</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -31353,7 +31353,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45755.29065972222</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -31477,7 +31477,7 @@
         <v>44373</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -31534,7 +31534,7 @@
         <v>45216</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>45209.55802083333</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31710,7 +31710,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31772,7 +31772,7 @@
         <v>45174</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31829,7 +31829,7 @@
         <v>45189.84020833333</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31886,7 +31886,7 @@
         <v>45825</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         <v>45170.45482638889</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -32000,7 +32000,7 @@
         <v>44880</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>44526</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>45825</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>45079</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>45719.31196759259</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -32285,7 +32285,7 @@
         <v>45447</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>45488.47798611111</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -32399,7 +32399,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45266.45414351852</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>44876</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>44439</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>45049</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32684,7 +32684,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32741,7 +32741,7 @@
         <v>44994</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45730.32494212963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32922,7 +32922,7 @@
         <v>44468</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32984,7 +32984,7 @@
         <v>44749</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -33041,7 +33041,7 @@
         <v>44826</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>44529</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -33155,7 +33155,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -33212,7 +33212,7 @@
         <v>45390</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -33269,7 +33269,7 @@
         <v>44824</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -33326,7 +33326,7 @@
         <v>44496.5093287037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -33383,7 +33383,7 @@
         <v>45481</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>44546.67575231481</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -33497,7 +33497,7 @@
         <v>45705.66491898148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>45370.55523148148</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33673,7 +33673,7 @@
         <v>45776</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45827.38844907407</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33787,7 +33787,7 @@
         <v>45715</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33844,7 +33844,7 @@
         <v>45271.40059027778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>45099</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>44516</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45580.70136574074</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -34072,7 +34072,7 @@
         <v>45827.4165625</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -34129,7 +34129,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>44834</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -34243,7 +34243,7 @@
         <v>45442.59461805555</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -34300,7 +34300,7 @@
         <v>45715</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -34357,7 +34357,7 @@
         <v>45209</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45582</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45218.40142361111</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34595,7 +34595,7 @@
         <v>45827.45986111111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34652,7 +34652,7 @@
         <v>45826.38826388889</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34709,7 +34709,7 @@
         <v>45182</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>45827.45690972222</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34880,7 +34880,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34937,7 +34937,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34999,7 +34999,7 @@
         <v>45827.44914351852</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -35056,7 +35056,7 @@
         <v>45827.45063657407</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -35113,7 +35113,7 @@
         <v>45827.45379629629</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>44547.48429398148</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -35227,7 +35227,7 @@
         <v>45160.60979166667</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>45827.40579861111</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -35341,7 +35341,7 @@
         <v>45827.47229166667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44939</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45121.60563657407</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45134</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45152.54458333334</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45168</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35683,7 +35683,7 @@
         <v>45826.38912037037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45827.46381944444</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35797,7 +35797,7 @@
         <v>45831.30805555556</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35854,7 +35854,7 @@
         <v>44882</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35911,7 +35911,7 @@
         <v>45831</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>44564.80535879629</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45152</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -36087,7 +36087,7 @@
         <v>45197.62081018519</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>44999.48005787037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44819</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>45180.46920138889</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44260</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -36377,7 +36377,7 @@
         <v>45252</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -36496,7 +36496,7 @@
         <v>44991.57855324074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -36553,7 +36553,7 @@
         <v>45715.6405787037</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45575</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>45348.39001157408</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45016</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36843,7 +36843,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45569</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45831.51925925926</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45406</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -37185,7 +37185,7 @@
         <v>45833.32947916666</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>45833</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>45834.56986111111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -37356,7 +37356,7 @@
         <v>45834.53106481482</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>45834.566875</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>45391.33994212963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -37584,7 +37584,7 @@
         <v>45257.7815625</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45834.65643518518</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37703,7 +37703,7 @@
         <v>45838.53700231481</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45693.5546875</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37817,7 +37817,7 @@
         <v>45693.55793981482</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37874,7 +37874,7 @@
         <v>45247</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44215</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37988,7 +37988,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -38050,7 +38050,7 @@
         <v>44999</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45259.37826388889</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -38164,7 +38164,7 @@
         <v>45505</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45554.4112037037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -38340,7 +38340,7 @@
         <v>45455.5603587963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45845.63357638889</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -38511,7 +38511,7 @@
         <v>45845.58313657407</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45340.86449074074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38625,7 +38625,7 @@
         <v>45729.46997685185</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
         <v>45019.36079861111</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45730.32915509259</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>45730.33262731481</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>44995</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45408.4359837963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45335</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45887.65018518519</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45884.5909375</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45168</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45842.68615740741</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -39329,7 +39329,7 @@
         <v>45884.45627314815</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -39443,7 +39443,7 @@
         <v>45843.54559027778</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         <v>45842.68381944444</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>45420.39489583333</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -39614,7 +39614,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39676,7 +39676,7 @@
         <v>45889.67118055555</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39733,7 +39733,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>44725</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>45629.43613425926</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>45714.74952546296</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39966,7 +39966,7 @@
         <v>45026</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>45161.48927083334</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -40137,7 +40137,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -40194,7 +40194,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>45894.65247685185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>45895.51850694444</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -40365,7 +40365,7 @@
         <v>45248</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>44685.48431712963</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -40479,7 +40479,7 @@
         <v>45092</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -40536,7 +40536,7 @@
         <v>44732</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>44300</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45054</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40712,7 +40712,7 @@
         <v>45091.65386574074</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40769,7 +40769,7 @@
         <v>45260.47619212963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>45260.47771990741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45901.66907407407</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45901.66547453704</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45096.90421296296</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45273</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45901</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -41354,7 +41354,7 @@
         <v>45484.55672453704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>45168</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -41468,7 +41468,7 @@
         <v>45903.67501157407</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -41525,7 +41525,7 @@
         <v>44893</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -41587,7 +41587,7 @@
         <v>44375</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>45538</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41701,7 +41701,7 @@
         <v>45439.58288194444</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>44258</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41929,7 +41929,7 @@
         <v>45902.32299768519</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -42043,7 +42043,7 @@
         <v>45903.70535879629</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -42100,7 +42100,7 @@
         <v>44966</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -42157,7 +42157,7 @@
         <v>45153</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -42214,7 +42214,7 @@
         <v>45903.49077546296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -42271,7 +42271,7 @@
         <v>45695.55989583334</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>45071</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45905.43545138889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>45156</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45309.80746527778</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45733.54085648148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45888</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42742,7 +42742,7 @@
         <v>45048.37384259259</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42799,7 +42799,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>45618</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42970,7 +42970,7 @@
         <v>45726.47065972222</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45726.56298611111</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>45909.54929398148</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -43146,7 +43146,7 @@
         <v>44565</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45909.56019675926</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>45225.76035879629</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45909.55575231482</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>45013.3293287037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>44655</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>44862</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -43607,7 +43607,7 @@
         <v>45909.54364583334</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43664,7 +43664,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43721,7 +43721,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43778,7 +43778,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43835,7 +43835,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43897,7 +43897,7 @@
         <v>45908</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43954,7 +43954,7 @@
         <v>45247</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>44438</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45754.50134259259</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45910.45300925926</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -44187,7 +44187,7 @@
         <v>45911.45987268518</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>45019.37908564815</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -44301,7 +44301,7 @@
         <v>45054</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -44358,7 +44358,7 @@
         <v>45908</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -44415,7 +44415,7 @@
         <v>44530</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -44472,7 +44472,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -44529,7 +44529,7 @@
         <v>45250.44482638889</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44586,7 +44586,7 @@
         <v>45681.58489583333</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44643,7 +44643,7 @@
         <v>45681.59599537037</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>44252</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45769.41255787037</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>45624.98180555556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44881,7 +44881,7 @@
         <v>45771.4725925926</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44943,7 +44943,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -45000,7 +45000,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>45547.37052083333</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -45114,7 +45114,7 @@
         <v>44470</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -45171,7 +45171,7 @@
         <v>45908</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45908</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -45285,7 +45285,7 @@
         <v>45912.65081018519</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>44971.36787037037</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -45399,7 +45399,7 @@
         <v>45915.34211805555</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -45456,7 +45456,7 @@
         <v>45908</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -45513,7 +45513,7 @@
         <v>45908</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>45841</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45627,7 +45627,7 @@
         <v>45908</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45684,7 +45684,7 @@
         <v>45638.49185185185</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45746,7 +45746,7 @@
         <v>45238</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45808,7 +45808,7 @@
         <v>45216.54601851852</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45744</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>45477.42023148148</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -46036,7 +46036,7 @@
         <v>45646.56480324074</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -46093,7 +46093,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>45905</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -46207,7 +46207,7 @@
         <v>45905</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -46264,7 +46264,7 @@
         <v>45841</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -46321,7 +46321,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -46378,7 +46378,7 @@
         <v>45248.819375</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -46435,7 +46435,7 @@
         <v>45916.50309027778</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -46549,7 +46549,7 @@
         <v>45916.54130787037</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46606,7 +46606,7 @@
         <v>45190.34791666667</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46663,7 +46663,7 @@
         <v>45918</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46720,7 +46720,7 @@
         <v>45318.64234953704</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46777,7 +46777,7 @@
         <v>45918</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45427</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46891,7 +46891,7 @@
         <v>45129.79834490741</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>45841</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -47062,7 +47062,7 @@
         <v>45741.47032407407</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -47124,7 +47124,7 @@
         <v>45698.611875</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -47181,7 +47181,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -47238,7 +47238,7 @@
         <v>45918</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -47295,7 +47295,7 @@
         <v>44113</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -47357,7 +47357,7 @@
         <v>44725</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -47414,7 +47414,7 @@
         <v>45755.30921296297</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -47471,7 +47471,7 @@
         <v>45755.31265046296</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -47528,7 +47528,7 @@
         <v>45755.31439814815</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -47585,7 +47585,7 @@
         <v>45923.5972337963</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47642,7 +47642,7 @@
         <v>45923.5996875</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47699,7 +47699,7 @@
         <v>45713.373125</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47761,7 +47761,7 @@
         <v>45923.45716435185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47818,7 +47818,7 @@
         <v>44999.36128472222</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47875,7 +47875,7 @@
         <v>45923.64208333333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>44928.4900462963</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47989,7 +47989,7 @@
         <v>44928</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -48051,7 +48051,7 @@
         <v>45923.60203703704</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -48108,7 +48108,7 @@
         <v>45923.60820601852</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -48165,7 +48165,7 @@
         <v>45923.58523148148</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -48222,7 +48222,7 @@
         <v>45923.61215277778</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -48279,7 +48279,7 @@
         <v>45923.61527777778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -48336,7 +48336,7 @@
         <v>45923.58434027778</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>45923.61694444445</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -48450,7 +48450,7 @@
         <v>45923.64820601852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -48507,7 +48507,7 @@
         <v>45881.60173611111</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -48564,7 +48564,7 @@
         <v>45923.59324074074</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48621,7 +48621,7 @@
         <v>45922.62423611111</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45923.90313657407</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45923.60518518519</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>45923.64613425926</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48849,7 +48849,7 @@
         <v>45880.63050925926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48906,7 +48906,7 @@
         <v>45505</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>45505</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -49020,7 +49020,7 @@
         <v>45852.91453703704</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45924.44417824074</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -49134,7 +49134,7 @@
         <v>45924.43762731482</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -49191,7 +49191,7 @@
         <v>45925.64373842593</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -49253,7 +49253,7 @@
         <v>45925.6472337963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>45925.64199074074</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45925.64988425926</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45925.65148148148</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -49501,7 +49501,7 @@
         <v>45925.64577546297</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>

--- a/Översikt HULTSFRED.xlsx
+++ b/Översikt HULTSFRED.xlsx
@@ -567,7 +567,7 @@
         <v>44468</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>44175</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45477.35888888889</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>45541.5456712963</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>45399</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45541.52103009259</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>45575</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>44474</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>44258</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>44551</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44224</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>44641</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>45026</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>45400</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45369.35270833333</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>44822</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2091,7 +2091,7 @@
         <v>44490</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44280</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44917.42984953704</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2353,7 +2353,7 @@
         <v>44278</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2439,7 +2439,7 @@
         <v>44235</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
         <v>45113.60486111111</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44468</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>44235</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>45810.41737268519</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>45466.63329861111</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45723.44277777777</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>44559</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45385</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44455</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3328,7 +3328,7 @@
         <v>44519.98922453704</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3413,7 +3413,7 @@
         <v>44295</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>44341</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>44397.6375462963</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44883.45847222222</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>45324</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>45399</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         <v>45393.63238425926</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>45595</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>45690.4250925926</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45399</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4296,7 +4296,7 @@
         <v>45904.5654050926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>45400</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>44876</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45450</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45009.35950231482</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         <v>45328</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>45594.41554398148</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45917.35021990741</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>44417</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45216.47987268519</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5171,7 +5171,7 @@
         <v>45147</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45225.75832175926</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>45690.42671296297</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45702.46353009259</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>44980</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>45568.38174768518</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>45016</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>45629.34431712963</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>45635.37515046296</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>45566</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>44942</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>45755.3155787037</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45604.64533564815</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>45755.30336805555</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>45798.3421875</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>45810.43359953703</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>45810.41100694444</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6652,7 +6652,7 @@
         <v>44319</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44526</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>45169.50775462963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6915,7 +6915,7 @@
         <v>45835.38121527778</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7000,7 +7000,7 @@
         <v>45191</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>45239</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44193.83646990741</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         <v>44270.60216435185</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44229</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44203.65149305556</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
         <v>44353</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44337</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -7583,7 +7583,7 @@
         <v>44609.71396990741</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>44385.34373842592</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>44477</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         <v>44449</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>44564</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>44827</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44827.63002314815</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>44193</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44215</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         <v>44833</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8153,7 +8153,7 @@
         <v>44193</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44520.0127662037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44151</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v>44356.47372685185</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>44137</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>44452.60662037037</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44564</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>44252</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>44249</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>44608</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>44385.36721064815</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>44676</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>44110</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>44480</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8971,7 +8971,7 @@
         <v>44134</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44375</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>44712.57193287037</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         <v>44223</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>44809.4018287037</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44385.31377314815</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>44831</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         <v>44532.64408564815</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         <v>44536</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>44839.48378472222</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -9546,7 +9546,7 @@
         <v>44490.51148148148</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9603,7 +9603,7 @@
         <v>44468</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9665,7 +9665,7 @@
         <v>44482</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>44700.38892361111</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>44705</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>44673</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>44631.46762731481</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>44490</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44375</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>44831</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
         <v>44831.75778935185</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         <v>44179</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44456</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44106</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>44295</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>44308</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44186.34966435185</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -10535,7 +10535,7 @@
         <v>44488.42239583333</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>44216</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>44582</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>44186</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
         <v>44126</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v>44111.87048611111</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44146</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         <v>44182.55774305556</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44274</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>44833</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>44172</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>44223</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
         <v>44368.45892361111</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44266.58711805556</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -11333,7 +11333,7 @@
         <v>44420</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>44375</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>44594</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>44594</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44831.31585648148</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44203</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44432</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         <v>44223</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         <v>44106.40355324074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11846,7 +11846,7 @@
         <v>44452.59549768519</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>44462.45162037037</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>44182</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>44526.35113425926</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>44490.5975925926</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>44132.38440972222</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>44420</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>44438</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         <v>44447</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>44811</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>44357.37903935185</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -12478,7 +12478,7 @@
         <v>44428.88928240741</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>44296.53390046296</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>44827</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>44314</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12706,7 +12706,7 @@
         <v>44473</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>44519.98100694444</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44519.99180555555</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>44520.006875</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>44130.37449074074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44614</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44526</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>44532</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>44532.58314814815</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44201</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>44683</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>44643</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -13390,7 +13390,7 @@
         <v>44490.34951388889</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44263</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>44278</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13561,7 +13561,7 @@
         <v>44320</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13618,7 +13618,7 @@
         <v>44713</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>44426</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>44482</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13789,7 +13789,7 @@
         <v>44743.57672453704</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>44712</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>44419</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>44645</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -14017,7 +14017,7 @@
         <v>44612</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>44350.91193287037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44434</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>44794</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -14250,7 +14250,7 @@
         <v>45618</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>45406</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -14364,7 +14364,7 @@
         <v>45050.42804398148</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45719.31096064814</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -14478,7 +14478,7 @@
         <v>45335</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45335.45155092593</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14592,7 +14592,7 @@
         <v>45340.92813657408</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45340.93671296296</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14706,7 +14706,7 @@
         <v>45216</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14763,7 +14763,7 @@
         <v>44552</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>45197.60594907407</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44532</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14934,7 +14934,7 @@
         <v>44749</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45247</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44617.44810185185</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -15105,7 +15105,7 @@
         <v>45174</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -15162,7 +15162,7 @@
         <v>44531.36721064815</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>44781.91173611111</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -15276,7 +15276,7 @@
         <v>44834</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -15333,7 +15333,7 @@
         <v>45715.64556712963</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>44755</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>44274.57768518518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>45714.74612268519</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>45359.35763888889</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15628,7 +15628,7 @@
         <v>44484</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>45702.47150462963</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15747,7 +15747,7 @@
         <v>45079</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>44375</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15861,7 +15861,7 @@
         <v>44741</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>45744</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44593</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44552.67385416666</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>44386</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -16146,7 +16146,7 @@
         <v>44975.87836805556</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>44420</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -16260,7 +16260,7 @@
         <v>44441</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -16317,7 +16317,7 @@
         <v>44496</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>45328.46377314815</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>44188</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45427</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44686</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44151</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44901</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>44537.4409375</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>44825.34015046297</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45168.62385416667</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45209</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16954,7 +16954,7 @@
         <v>44705.43685185185</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -17011,7 +17011,7 @@
         <v>44151</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45252.44798611111</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>45895.51850694444</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45755.29387731481</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>45852.91319444445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -17306,7 +17306,7 @@
         <v>45541.52309027778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45477.3924537037</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>45420</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44939</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45152.34190972222</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45324</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17673,7 +17673,7 @@
         <v>44215</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>45391.33564814815</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>45615.62094907407</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45180</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>45412.30461805555</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>45412.60458333333</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -18015,7 +18015,7 @@
         <v>45597</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45360.69721064815</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45748.37739583333</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45129.80059027778</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>45524.63563657407</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>44816.82284722223</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>45691.36478009259</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>45512</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>44880</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45901.66907407407</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45902.32299768519</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>44970.58731481482</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>45559.50409722222</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>45901.66547453704</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18828,7 +18828,7 @@
         <v>45901</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45568.35815972222</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>44928</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>44484</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>45477.36623842592</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -19123,7 +19123,7 @@
         <v>45477.37200231481</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>44375</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45225</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45749.37798611111</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>44651</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45903.49077546296</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -19465,7 +19465,7 @@
         <v>45903.67501157407</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -19522,7 +19522,7 @@
         <v>45755.29855324074</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>45903.70535879629</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>45723.4478125</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>44438</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44862</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45615.59752314815</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45092</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45185.6368287037</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>44963.62231481481</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44655</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>44825.32336805556</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -20164,7 +20164,7 @@
         <v>45621.44763888889</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45271.41395833333</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>44118</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45813.44929398148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44610</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>45888</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>44994.45324074074</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45905.43545138889</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20630,7 +20630,7 @@
         <v>45135.42358796296</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45813.52047453704</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45909.55575231482</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45909.54364583334</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45909.56019675926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>44502</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45573.45638888889</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45575</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>45910.45300925926</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45147.70241898148</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45618</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45273.28496527778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44903.47134259259</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -21376,7 +21376,7 @@
         <v>45909.54929398148</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -21433,7 +21433,7 @@
         <v>45834.54039351852</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -21490,7 +21490,7 @@
         <v>44235.39321759259</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45841</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45267.28141203704</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45477.36236111111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>44830.4331712963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45153</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44831</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45168</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45153.62142361111</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
         <v>44992.64321759259</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45905</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45905</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -22184,7 +22184,7 @@
         <v>45908</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>45908</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
         <v>45908</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -22355,7 +22355,7 @@
         <v>45908</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>44526</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -22469,7 +22469,7 @@
         <v>45908</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45911.45987268518</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>44183.62951388889</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45714.74789351852</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45912.65081018519</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>44824</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45412.45262731481</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>44470</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>44474.46346064815</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44998.50371527778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44530.34732638889</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -23106,7 +23106,7 @@
         <v>45908</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -23163,7 +23163,7 @@
         <v>45908</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -23220,7 +23220,7 @@
         <v>45841</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -23277,7 +23277,7 @@
         <v>45610.67653935185</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45439.56127314815</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45360.69631944445</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -23458,7 +23458,7 @@
         <v>45414</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44498.49251157408</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45307</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45743.3609375</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23686,7 +23686,7 @@
         <v>45085</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45916.50309027778</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45372.51892361111</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23857,7 +23857,7 @@
         <v>45631</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>45081.91804398148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23971,7 +23971,7 @@
         <v>45916.54130787037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45355</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -24085,7 +24085,7 @@
         <v>45573.00284722223</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>45915.34211805555</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45873.39606481481</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -24256,7 +24256,7 @@
         <v>44882</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>45041.6187037037</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>45695.56664351852</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -24432,7 +24432,7 @@
         <v>44482.36085648148</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -24489,7 +24489,7 @@
         <v>44916.57162037037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>44868.66078703704</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24603,7 +24603,7 @@
         <v>44592</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24660,7 +24660,7 @@
         <v>44994.54207175926</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>45610.63998842592</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24774,7 +24774,7 @@
         <v>44881.37020833333</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>44952.49959490741</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24888,7 +24888,7 @@
         <v>45635.38275462963</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45638.48775462963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -25007,7 +25007,7 @@
         <v>45081.89592592593</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -25064,7 +25064,7 @@
         <v>45169.61795138889</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -25121,7 +25121,7 @@
         <v>44964.61778935185</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>44970.8662962963</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -25235,7 +25235,7 @@
         <v>44999</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45610.66920138889</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>44831.66966435185</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45918</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45918</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45481</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25577,7 +25577,7 @@
         <v>45180</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25639,7 +25639,7 @@
         <v>45703.40883101852</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>44994.45459490741</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>45642.5578125</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45016.51652777778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45152</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45054</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25986,7 +25986,7 @@
         <v>45918</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -26043,7 +26043,7 @@
         <v>45538</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45104.82601851852</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -26157,7 +26157,7 @@
         <v>45169.62340277778</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45070.64072916667</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>44981.40186342593</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -26328,7 +26328,7 @@
         <v>45826.52912037037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -26385,7 +26385,7 @@
         <v>45703.40652777778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -26447,7 +26447,7 @@
         <v>44995</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -26504,7